--- a/raw/Cải tiến nhập dữ liệu chung vào file MPnew 09.06.2026.xlsx
+++ b/raw/Cải tiến nhập dữ liệu chung vào file MPnew 09.06.2026.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kdcf-my.sharepoint.com/personal/vinh_bd_dtvn_kyocera_com/Documents/Microsoft Teams Chat Files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sandbox\MP2027\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="90" documentId="13_ncr:1_{223E63D1-030C-4F31-9354-B409472DF7C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D686DE6-E699-4859-8357-9210D34BE42E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D16C6D-1A5B-466D-BEB3-7BE2A572363A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="703" firstSheet="6" activeTab="7" xr2:uid="{EF1EAAF0-F653-4155-9EE7-30B01C7CE0E3}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="15600" tabRatio="703" firstSheet="5" activeTab="7" xr2:uid="{EF1EAAF0-F653-4155-9EE7-30B01C7CE0E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2871,7 +2871,7 @@
     <numFmt numFmtId="164" formatCode="0_ "/>
     <numFmt numFmtId="165" formatCode="#,##0."/>
   </numFmts>
-  <fonts count="49">
+  <fonts count="49" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3213,7 +3213,7 @@
       <name val="Tahoma"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3259,12 +3259,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3331,7 +3325,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3471,6 +3465,9 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3480,26 +3477,16 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="46" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="4" xr:uid="{9DC64E9C-35A6-4927-BB95-C832AE601F6D}"/>
+    <cellStyle name="Siêu kết nối" xfId="1" builtinId="8"/>
     <cellStyle name="標準 2" xfId="3" xr:uid="{662A8341-A924-41D5-83D2-794F70883A65}"/>
     <cellStyle name="標準_★予定用採算表フォーム（製造課用）" xfId="2" xr:uid="{01A64E73-DBB2-4F74-AF40-9610980FF44F}"/>
     <cellStyle name="標準_KDTVN 2012年9月1日付原価センタ" xfId="5" xr:uid="{068AA743-FB0B-475F-BB05-35A7912D3FD9}"/>
@@ -3770,8 +3757,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="65232" y="694799"/>
-          <a:ext cx="18861367" cy="6038231"/>
+          <a:off x="68407" y="732899"/>
+          <a:ext cx="18070792" cy="6470031"/>
           <a:chOff x="146050" y="606476"/>
           <a:chExt cx="18931794" cy="5881213"/>
         </a:xfrm>
@@ -5050,8 +5037,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="431131" y="17219707"/>
-          <a:ext cx="5556131" cy="2552262"/>
+          <a:off x="434306" y="18463000"/>
+          <a:ext cx="5284015" cy="2776379"/>
           <a:chOff x="348954" y="16263471"/>
           <a:chExt cx="5556131" cy="2552262"/>
         </a:xfrm>
@@ -13904,8 +13891,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="750066" y="13267018"/>
-          <a:ext cx="2974022" cy="3285822"/>
+          <a:off x="720184" y="14062635"/>
+          <a:ext cx="2847022" cy="3487528"/>
           <a:chOff x="747078" y="14573250"/>
           <a:chExt cx="2974022" cy="3258928"/>
         </a:xfrm>
@@ -14371,8 +14358,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1259140" y="23029689"/>
-          <a:ext cx="9887770" cy="848179"/>
+          <a:off x="1199376" y="24295954"/>
+          <a:ext cx="9417123" cy="829502"/>
           <a:chOff x="1253164" y="25525239"/>
           <a:chExt cx="10090970" cy="846311"/>
         </a:xfrm>
@@ -14797,8 +14784,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="546100" y="39837516"/>
-          <a:ext cx="9359900" cy="3065411"/>
+          <a:off x="546100" y="41787339"/>
+          <a:ext cx="8889253" cy="3255911"/>
           <a:chOff x="628650" y="32981010"/>
           <a:chExt cx="9334500" cy="3040011"/>
         </a:xfrm>
@@ -16487,74 +16474,74 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCAFCF0F-6187-4E87-BF1F-8C8A3070C713}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:B55"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="2"/>
-    <col min="2" max="2" width="26.36328125" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="8.7265625" style="2"/>
+    <col min="1" max="1" width="8.7109375" style="2"/>
+    <col min="2" max="2" width="26.42578125" style="2" customWidth="1"/>
+    <col min="3" max="16384" width="8.7109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="20">
+    <row r="1" spans="1:1" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="17.5">
+    <row r="3" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="17.5">
+    <row r="39" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B40" s="10" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="32.5" customHeight="1"/>
-    <row r="42" spans="1:2" ht="14.5">
+    <row r="41" spans="1:2" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B42" s="14" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="32.5" customHeight="1"/>
-    <row r="44" spans="1:2">
+    <row r="43" spans="1:2" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B44" s="10" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="28.5" customHeight="1"/>
-    <row r="46" spans="1:2">
+    <row r="45" spans="1:2" ht="28.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B46" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="34.5" customHeight="1"/>
-    <row r="48" spans="1:2" ht="38.15" customHeight="1"/>
-    <row r="50" spans="1:2" ht="17.5">
+    <row r="47" spans="1:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:2" ht="38.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B52" s="12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B53" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B54" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B55" s="2" t="s">
         <v>11</v>
       </c>
@@ -16576,21 +16563,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05E105BB-F502-4B2C-A8EC-3B5755086A6D}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:E66"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.6328125" style="35" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" style="35" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" style="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.90625" style="37" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.26953125" style="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.85546875" style="37" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="36"/>
-    <col min="6" max="6" width="10.90625" style="36" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.36328125" style="36" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" style="36" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" style="36" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="36"/>
-    <col min="9" max="9" width="13.36328125" style="36" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="36" customWidth="1"/>
     <col min="10" max="16384" width="9" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.5">
+    <row r="1" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>173</v>
       </c>
@@ -16607,7 +16594,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="14.5">
+    <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1412000004</v>
       </c>
@@ -16624,7 +16611,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="14.5">
+    <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1412000005</v>
       </c>
@@ -16641,7 +16628,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="14.5">
+    <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1412000081</v>
       </c>
@@ -16658,7 +16645,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="14.5">
+    <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1412000066</v>
       </c>
@@ -16675,7 +16662,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="14.5">
+    <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1412000034</v>
       </c>
@@ -16692,7 +16679,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="14.5">
+    <row r="7" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1412000056</v>
       </c>
@@ -16709,7 +16696,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="14.5">
+    <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1412000050</v>
       </c>
@@ -16726,7 +16713,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="14.5">
+    <row r="9" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1412000077</v>
       </c>
@@ -16743,7 +16730,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="14.5">
+    <row r="10" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1412000083</v>
       </c>
@@ -16760,7 +16747,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="14.5">
+    <row r="11" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1412000057</v>
       </c>
@@ -16777,7 +16764,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="14.5">
+    <row r="12" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1412000078</v>
       </c>
@@ -16794,7 +16781,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="14.5">
+    <row r="13" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1412000062</v>
       </c>
@@ -16811,7 +16798,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="14.5">
+    <row r="14" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>1412000036</v>
       </c>
@@ -16828,7 +16815,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="14.5">
+    <row r="15" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1412000103</v>
       </c>
@@ -16845,7 +16832,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="14.5">
+    <row r="16" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>1412000063</v>
       </c>
@@ -16862,7 +16849,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="14.5">
+    <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1412000048</v>
       </c>
@@ -16879,7 +16866,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="14.5">
+    <row r="18" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>1412000055</v>
       </c>
@@ -16896,7 +16883,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="14.5">
+    <row r="19" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>1412000073</v>
       </c>
@@ -16913,7 +16900,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="14.5">
+    <row r="20" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>1412000008</v>
       </c>
@@ -16930,7 +16917,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="14.5">
+    <row r="21" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>1412000094</v>
       </c>
@@ -16947,7 +16934,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="14.5">
+    <row r="22" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>1412000080</v>
       </c>
@@ -16964,7 +16951,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="14.5">
+    <row r="23" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>1412000087</v>
       </c>
@@ -16981,7 +16968,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="14.5">
+    <row r="24" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>1412000088</v>
       </c>
@@ -16998,7 +16985,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="14.5">
+    <row r="25" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>1412000072</v>
       </c>
@@ -17015,7 +17002,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="14.5">
+    <row r="26" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>1412000053</v>
       </c>
@@ -17032,7 +17019,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="14.5">
+    <row r="27" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>1412000104</v>
       </c>
@@ -17049,7 +17036,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="14.5">
+    <row r="28" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>1412000105</v>
       </c>
@@ -17066,7 +17053,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="14.5">
+    <row r="29" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>1412000075</v>
       </c>
@@ -17083,7 +17070,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="14.5">
+    <row r="30" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>1412000044</v>
       </c>
@@ -17100,7 +17087,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="14.5">
+    <row r="31" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>1412000054</v>
       </c>
@@ -17117,7 +17104,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="14.5">
+    <row r="32" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>1412000010</v>
       </c>
@@ -17134,7 +17121,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="14.5">
+    <row r="33" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>1412000013</v>
       </c>
@@ -17151,7 +17138,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="14.5">
+    <row r="34" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>1412000092</v>
       </c>
@@ -17168,7 +17155,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="14.5">
+    <row r="35" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>1412000035</v>
       </c>
@@ -17185,7 +17172,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="14.5">
+    <row r="36" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A36" s="58">
         <v>1412000108</v>
       </c>
@@ -17202,7 +17189,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="14.5">
+    <row r="37" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>1412000006</v>
       </c>
@@ -17219,7 +17206,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="14.5">
+    <row r="38" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>1412000089</v>
       </c>
@@ -17236,7 +17223,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="14.5">
+    <row r="39" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>1412000040</v>
       </c>
@@ -17253,7 +17240,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="14.5">
+    <row r="40" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>1412000106</v>
       </c>
@@ -17270,7 +17257,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="14.5">
+    <row r="41" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>1412000039</v>
       </c>
@@ -17287,7 +17274,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="14.5">
+    <row r="42" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>1412000016</v>
       </c>
@@ -17304,7 +17291,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="14.5">
+    <row r="43" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>1412000069</v>
       </c>
@@ -17321,7 +17308,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="14.5">
+    <row r="44" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>1412000084</v>
       </c>
@@ -17338,7 +17325,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="14.5">
+    <row r="45" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>1412000018</v>
       </c>
@@ -17355,7 +17342,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="14.5">
+    <row r="46" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>1412000019</v>
       </c>
@@ -17372,7 +17359,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="14.5">
+    <row r="47" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>1412000058</v>
       </c>
@@ -17389,7 +17376,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="14.5">
+    <row r="48" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>1412000042</v>
       </c>
@@ -17406,7 +17393,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="14.5">
+    <row r="49" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>1412000021</v>
       </c>
@@ -17423,7 +17410,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="14.5">
+    <row r="50" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>1412000070</v>
       </c>
@@ -17440,7 +17427,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="14.5">
+    <row r="51" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>1412000022</v>
       </c>
@@ -17457,7 +17444,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="14.5">
+    <row r="52" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>1412000024</v>
       </c>
@@ -17474,7 +17461,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="14.5">
+    <row r="53" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>1412000025</v>
       </c>
@@ -17491,7 +17478,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="14.5">
+    <row r="54" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>1412000026</v>
       </c>
@@ -17508,7 +17495,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="14.5">
+    <row r="55" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>1412000093</v>
       </c>
@@ -17525,7 +17512,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="14.5">
+    <row r="56" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>1412000028</v>
       </c>
@@ -17542,7 +17529,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="14.5">
+    <row r="57" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>1412000029</v>
       </c>
@@ -17559,7 +17546,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="14.5">
+    <row r="58" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>1412000091</v>
       </c>
@@ -17576,7 +17563,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="14.5">
+    <row r="59" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>1412000086</v>
       </c>
@@ -17593,7 +17580,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="14.5">
+    <row r="60" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>832</v>
       </c>
@@ -17606,7 +17593,7 @@
       <c r="D60"/>
       <c r="E60"/>
     </row>
-    <row r="61" spans="1:5" ht="14.5">
+    <row r="61" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>1412000030</v>
       </c>
@@ -17623,7 +17610,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="14.5">
+    <row r="62" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>1412000098</v>
       </c>
@@ -17640,7 +17627,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="14.5">
+    <row r="63" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>1412000096</v>
       </c>
@@ -17657,7 +17644,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="14.5">
+    <row r="64" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>1412000099</v>
       </c>
@@ -17674,7 +17661,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="14.5">
+    <row r="65" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>1412000100</v>
       </c>
@@ -17691,7 +17678,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="14.5">
+    <row r="66" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>1412000101</v>
       </c>
@@ -17722,459 +17709,459 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:M339"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="8.7265625" style="2"/>
+    <col min="1" max="16384" width="8.7109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="25">
+    <row r="1" spans="1:1" ht="25.5" x14ac:dyDescent="0.35">
       <c r="A1" s="41" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:1" s="47" customFormat="1" ht="20.5">
+    <row r="2" spans="1:1" s="47" customFormat="1" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A2" s="46" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:1" s="47" customFormat="1"/>
-    <row r="4" spans="1:1" s="47" customFormat="1"/>
-    <row r="5" spans="1:1" s="47" customFormat="1"/>
-    <row r="6" spans="1:1" s="47" customFormat="1"/>
-    <row r="7" spans="1:1" s="47" customFormat="1"/>
-    <row r="8" spans="1:1" s="47" customFormat="1"/>
-    <row r="9" spans="1:1" s="47" customFormat="1"/>
-    <row r="10" spans="1:1" s="47" customFormat="1"/>
-    <row r="11" spans="1:1" s="47" customFormat="1"/>
-    <row r="12" spans="1:1" s="47" customFormat="1"/>
-    <row r="13" spans="1:1" s="47" customFormat="1"/>
-    <row r="14" spans="1:1" s="47" customFormat="1"/>
-    <row r="15" spans="1:1" s="47" customFormat="1"/>
-    <row r="16" spans="1:1" s="47" customFormat="1" ht="20.5">
+    <row r="3" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:1" s="47" customFormat="1" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A16" s="46" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" s="47" customFormat="1"/>
-    <row r="18" s="47" customFormat="1"/>
-    <row r="19" s="47" customFormat="1"/>
-    <row r="20" s="47" customFormat="1"/>
-    <row r="21" s="47" customFormat="1"/>
-    <row r="22" s="47" customFormat="1"/>
-    <row r="23" s="47" customFormat="1"/>
-    <row r="24" s="47" customFormat="1"/>
-    <row r="25" s="47" customFormat="1"/>
-    <row r="26" s="47" customFormat="1"/>
-    <row r="27" s="47" customFormat="1"/>
-    <row r="28" s="47" customFormat="1"/>
-    <row r="29" s="47" customFormat="1"/>
-    <row r="30" s="47" customFormat="1"/>
-    <row r="31" s="47" customFormat="1"/>
-    <row r="32" s="47" customFormat="1"/>
-    <row r="33" spans="1:1" s="47" customFormat="1"/>
-    <row r="34" spans="1:1" s="47" customFormat="1"/>
-    <row r="35" spans="1:1" s="47" customFormat="1"/>
-    <row r="36" spans="1:1" s="47" customFormat="1"/>
-    <row r="37" spans="1:1" s="47" customFormat="1" ht="20.5">
+    <row r="17" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="18" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="19" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="20" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="21" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="22" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="23" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="24" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="25" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="26" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="27" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="28" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="29" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="30" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="31" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="32" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:1" s="47" customFormat="1" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A37" s="46" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:1" s="47" customFormat="1"/>
-    <row r="39" spans="1:1" s="47" customFormat="1"/>
-    <row r="40" spans="1:1" s="47" customFormat="1"/>
-    <row r="41" spans="1:1" s="47" customFormat="1"/>
-    <row r="42" spans="1:1" s="47" customFormat="1"/>
-    <row r="43" spans="1:1" s="47" customFormat="1"/>
-    <row r="44" spans="1:1" s="47" customFormat="1" ht="20.5">
+    <row r="38" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:1" s="47" customFormat="1" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A44" s="46" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:1" s="47" customFormat="1" ht="20.5">
+    <row r="45" spans="1:1" s="47" customFormat="1" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A45" s="48" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:1" s="47" customFormat="1">
+    <row r="46" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="47" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:1" s="47" customFormat="1"/>
-    <row r="48" spans="1:1" s="47" customFormat="1"/>
-    <row r="49" s="47" customFormat="1"/>
-    <row r="50" s="47" customFormat="1"/>
-    <row r="51" s="47" customFormat="1"/>
-    <row r="52" s="47" customFormat="1"/>
-    <row r="53" s="47" customFormat="1"/>
-    <row r="54" s="47" customFormat="1"/>
-    <row r="55" s="47" customFormat="1"/>
-    <row r="56" s="47" customFormat="1"/>
-    <row r="57" s="47" customFormat="1"/>
-    <row r="58" s="47" customFormat="1"/>
-    <row r="59" s="47" customFormat="1"/>
-    <row r="60" s="47" customFormat="1"/>
-    <row r="61" s="47" customFormat="1"/>
-    <row r="62" s="47" customFormat="1"/>
-    <row r="63" s="47" customFormat="1"/>
-    <row r="64" s="47" customFormat="1"/>
-    <row r="65" spans="1:1" s="47" customFormat="1"/>
-    <row r="66" spans="1:1" s="47" customFormat="1"/>
-    <row r="67" spans="1:1" s="47" customFormat="1"/>
-    <row r="68" spans="1:1" s="47" customFormat="1"/>
-    <row r="69" spans="1:1" s="47" customFormat="1"/>
-    <row r="70" spans="1:1" s="47" customFormat="1" ht="20.5">
+    <row r="47" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="49" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="50" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="51" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="52" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="53" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="54" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="55" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="56" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="57" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="58" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="59" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="60" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="61" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="62" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="63" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="64" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="1:1" s="47" customFormat="1" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A70" s="46" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="71" spans="1:1" s="47" customFormat="1"/>
-    <row r="72" spans="1:1" s="47" customFormat="1"/>
-    <row r="73" spans="1:1" s="47" customFormat="1"/>
-    <row r="74" spans="1:1" s="47" customFormat="1"/>
-    <row r="75" spans="1:1" s="47" customFormat="1"/>
-    <row r="76" spans="1:1" s="47" customFormat="1"/>
-    <row r="77" spans="1:1" s="47" customFormat="1"/>
-    <row r="78" spans="1:1" s="47" customFormat="1"/>
-    <row r="79" spans="1:1" s="47" customFormat="1"/>
-    <row r="80" spans="1:1" s="47" customFormat="1"/>
-    <row r="81" spans="1:1" s="47" customFormat="1"/>
-    <row r="82" spans="1:1" s="47" customFormat="1"/>
-    <row r="83" spans="1:1" s="47" customFormat="1"/>
-    <row r="84" spans="1:1" s="47" customFormat="1"/>
-    <row r="85" spans="1:1" s="47" customFormat="1"/>
-    <row r="86" spans="1:1" s="47" customFormat="1"/>
-    <row r="87" spans="1:1" s="47" customFormat="1"/>
-    <row r="88" spans="1:1" s="47" customFormat="1"/>
-    <row r="89" spans="1:1" s="47" customFormat="1"/>
-    <row r="90" spans="1:1" s="47" customFormat="1" ht="18">
+    <row r="71" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="1:1" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A90" s="49" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="91" spans="1:1" s="47" customFormat="1" ht="18">
+    <row r="91" spans="1:1" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A91" s="49" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="92" spans="1:1" s="47" customFormat="1"/>
-    <row r="93" spans="1:1" s="47" customFormat="1"/>
-    <row r="94" spans="1:1" s="47" customFormat="1"/>
-    <row r="95" spans="1:1" s="47" customFormat="1"/>
-    <row r="96" spans="1:1" s="47" customFormat="1"/>
-    <row r="97" spans="1:2" s="47" customFormat="1"/>
-    <row r="98" spans="1:2" s="47" customFormat="1"/>
-    <row r="99" spans="1:2" s="47" customFormat="1"/>
-    <row r="100" spans="1:2" s="47" customFormat="1"/>
-    <row r="101" spans="1:2" s="47" customFormat="1"/>
-    <row r="102" spans="1:2" s="47" customFormat="1"/>
-    <row r="103" spans="1:2" s="47" customFormat="1"/>
-    <row r="104" spans="1:2" s="47" customFormat="1"/>
-    <row r="105" spans="1:2" s="47" customFormat="1"/>
-    <row r="106" spans="1:2" s="47" customFormat="1"/>
-    <row r="107" spans="1:2" s="47" customFormat="1"/>
-    <row r="108" spans="1:2" s="47" customFormat="1"/>
-    <row r="109" spans="1:2" ht="18">
+    <row r="92" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="1:2" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="1:2" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="1:2" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="100" spans="1:2" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="1:2" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="1:2" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="1:2" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="1:2" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="1:2" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="1:2" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="1:2" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="1:2" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A109" s="40" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="110" spans="1:2" ht="16">
+    <row r="110" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B110" s="42" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="111" spans="1:2" ht="15.5">
+    <row r="111" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B111" s="50"/>
     </row>
-    <row r="112" spans="1:2" ht="15.5">
+    <row r="112" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="53" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="15.5">
+    <row r="113" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="53" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="15.5">
+    <row r="114" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="53" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="115" spans="1:2">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="3"/>
     </row>
-    <row r="116" spans="1:2" s="47" customFormat="1" ht="18">
+    <row r="116" spans="1:2" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A116" s="80" t="s">
         <v>27</v>
       </c>
       <c r="B116" s="80"/>
     </row>
-    <row r="117" spans="1:2" s="47" customFormat="1" ht="18">
+    <row r="117" spans="1:2" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A117" s="49" t="s">
         <v>28</v>
       </c>
       <c r="B117" s="80"/>
     </row>
-    <row r="118" spans="1:2" s="47" customFormat="1" ht="18">
+    <row r="118" spans="1:2" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A118" s="80"/>
       <c r="B118" s="80"/>
     </row>
-    <row r="119" spans="1:2" s="47" customFormat="1" ht="18">
+    <row r="119" spans="1:2" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A119" s="80"/>
       <c r="B119" s="80"/>
     </row>
-    <row r="120" spans="1:2" s="47" customFormat="1" ht="18">
+    <row r="120" spans="1:2" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A120" s="80"/>
       <c r="B120" s="80"/>
     </row>
-    <row r="121" spans="1:2" s="47" customFormat="1" ht="18">
+    <row r="121" spans="1:2" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A121" s="80"/>
       <c r="B121" s="80"/>
     </row>
-    <row r="122" spans="1:2" s="47" customFormat="1" ht="18">
+    <row r="122" spans="1:2" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A122" s="80"/>
       <c r="B122" s="80"/>
     </row>
-    <row r="123" spans="1:2" s="47" customFormat="1" ht="18">
+    <row r="123" spans="1:2" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A123" s="80"/>
       <c r="B123" s="80"/>
     </row>
-    <row r="124" spans="1:2" s="47" customFormat="1" ht="18">
+    <row r="124" spans="1:2" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A124" s="80"/>
       <c r="B124" s="80"/>
     </row>
-    <row r="125" spans="1:2" s="47" customFormat="1" ht="18">
+    <row r="125" spans="1:2" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A125" s="80"/>
       <c r="B125" s="80"/>
     </row>
-    <row r="126" spans="1:2" s="47" customFormat="1" ht="18">
+    <row r="126" spans="1:2" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A126" s="80"/>
       <c r="B126" s="81" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="127" spans="1:2" s="47" customFormat="1" ht="18">
+    <row r="127" spans="1:2" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A127" s="80"/>
       <c r="B127" s="82"/>
     </row>
-    <row r="128" spans="1:2" s="47" customFormat="1" ht="18">
+    <row r="128" spans="1:2" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A128" s="80"/>
       <c r="B128" s="82"/>
     </row>
-    <row r="129" spans="1:2" s="47" customFormat="1" ht="18">
+    <row r="129" spans="1:2" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A129" s="80"/>
       <c r="B129" s="82"/>
     </row>
-    <row r="130" spans="1:2" s="47" customFormat="1" ht="18">
+    <row r="130" spans="1:2" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A130" s="80"/>
       <c r="B130" s="82"/>
     </row>
-    <row r="131" spans="1:2" s="47" customFormat="1" ht="18">
+    <row r="131" spans="1:2" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A131" s="80"/>
       <c r="B131" s="82"/>
     </row>
-    <row r="132" spans="1:2" s="47" customFormat="1" ht="18">
+    <row r="132" spans="1:2" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A132" s="80"/>
       <c r="B132" s="82"/>
     </row>
-    <row r="133" spans="1:2" s="47" customFormat="1" ht="18">
+    <row r="133" spans="1:2" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A133" s="80"/>
       <c r="B133" s="82"/>
     </row>
-    <row r="134" spans="1:2" s="47" customFormat="1" ht="18">
+    <row r="134" spans="1:2" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A134" s="80"/>
       <c r="B134" s="82"/>
     </row>
-    <row r="135" spans="1:2" s="47" customFormat="1" ht="18">
+    <row r="135" spans="1:2" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A135" s="80"/>
       <c r="B135" s="82"/>
     </row>
-    <row r="136" spans="1:2" s="47" customFormat="1" ht="18">
+    <row r="136" spans="1:2" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A136" s="80"/>
       <c r="B136" s="82"/>
     </row>
-    <row r="137" spans="1:2" s="47" customFormat="1" ht="18">
+    <row r="137" spans="1:2" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A137" s="80"/>
       <c r="B137" s="82"/>
     </row>
-    <row r="138" spans="1:2" s="47" customFormat="1" ht="18">
+    <row r="138" spans="1:2" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A138" s="80"/>
       <c r="B138" s="83" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="139" spans="1:2" s="47" customFormat="1" ht="18">
+    <row r="139" spans="1:2" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A139" s="80"/>
       <c r="B139" s="47" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="140" spans="1:2" ht="18">
+    <row r="140" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A140" s="44"/>
       <c r="B140" s="56"/>
     </row>
-    <row r="141" spans="1:2" ht="18">
+    <row r="141" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A141" s="44"/>
       <c r="B141" s="56"/>
     </row>
-    <row r="142" spans="1:2" ht="18">
+    <row r="142" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A142" s="44"/>
       <c r="B142" s="44"/>
     </row>
-    <row r="143" spans="1:2" ht="18">
+    <row r="143" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A143" s="40" t="s">
         <v>32</v>
       </c>
       <c r="B143" s="44"/>
     </row>
-    <row r="144" spans="1:2" ht="18.5">
+    <row r="144" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A144" s="44"/>
       <c r="B144" s="45" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="145" spans="1:2" ht="18.5">
+    <row r="145" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A145" s="44"/>
       <c r="B145" s="45"/>
     </row>
-    <row r="146" spans="1:2" ht="18.5">
+    <row r="146" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A146" s="40" t="s">
         <v>33</v>
       </c>
       <c r="B146" s="45"/>
     </row>
-    <row r="147" spans="1:2" ht="18.5">
+    <row r="147" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A147" s="44"/>
       <c r="B147" s="51" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="149" spans="1:2" s="47" customFormat="1" ht="18">
+    <row r="149" spans="1:2" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A149" s="49" t="s">
         <v>34</v>
       </c>
       <c r="B149" s="80"/>
     </row>
-    <row r="150" spans="1:2" s="47" customFormat="1" ht="18.5">
+    <row r="150" spans="1:2" s="47" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A150" s="80"/>
       <c r="B150" s="84" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="152" spans="1:2" ht="17.5">
+    <row r="152" spans="1:2" ht="19.5" x14ac:dyDescent="0.35">
       <c r="A152" s="52" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="153" spans="1:2" ht="17.5">
+    <row r="153" spans="1:2" ht="19.5" x14ac:dyDescent="0.35">
       <c r="A153" s="52" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="156" spans="1:2" ht="17.5">
+    <row r="156" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A156" s="72" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="157" spans="1:2" ht="18">
+    <row r="157" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A157" s="73" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="158" spans="1:2" ht="18">
+    <row r="158" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A158" s="73" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="159" spans="1:2" ht="18">
+    <row r="159" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A159" s="73" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="160" spans="1:2" ht="18">
+    <row r="160" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A160" s="73" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="161" spans="1:1" ht="18">
+    <row r="161" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A161" s="73" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="162" spans="1:1" ht="18">
+    <row r="162" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A162" s="73" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="163" spans="1:1" ht="18">
+    <row r="163" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A163" s="73" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="164" spans="1:1" ht="18">
+    <row r="164" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A164" s="73" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="165" spans="1:1" ht="18">
+    <row r="165" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A165" s="73" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="166" spans="1:1" ht="18">
+    <row r="166" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A166" s="73" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="167" spans="1:1" ht="18">
+    <row r="167" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A167" s="73" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="168" spans="1:1" ht="18">
+    <row r="168" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A168" s="74" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="169" spans="1:1" ht="18">
+    <row r="169" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A169" s="74" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="171" spans="1:1" ht="17.5">
+    <row r="171" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A171" s="71" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="176" spans="1:1">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="177" spans="2:11">
+    <row r="177" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B177" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="179" spans="2:11" ht="14.5">
+    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H179" s="14" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="183" spans="2:11" ht="14.5">
+    <row r="183" spans="2:11" x14ac:dyDescent="0.25">
       <c r="K183" s="14" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="194" spans="1:7">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="89">
         <v>46271</v>
       </c>
     </row>
-    <row r="195" spans="1:7">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
         <v>1</v>
       </c>
@@ -18182,7 +18169,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="197" spans="1:7">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
         <v>2</v>
       </c>
@@ -18190,10 +18177,10 @@
         <v>57</v>
       </c>
     </row>
-    <row r="199" spans="1:7">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="85"/>
     </row>
-    <row r="200" spans="1:7">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" s="2">
         <v>3</v>
       </c>
@@ -18201,17 +18188,17 @@
         <v>58</v>
       </c>
     </row>
-    <row r="201" spans="1:7">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B201" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="202" spans="1:7">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B202" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="203" spans="1:7" ht="14.5">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B203" s="2" t="s">
         <v>61</v>
       </c>
@@ -18219,7 +18206,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="205" spans="1:7">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="2">
         <v>4</v>
       </c>
@@ -18227,7 +18214,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="14.5">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B206" s="3" t="s">
         <v>62</v>
       </c>
@@ -18235,7 +18222,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="208" spans="1:7">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
         <v>5</v>
       </c>
@@ -18243,12 +18230,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="209" spans="1:10">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B209" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="211" spans="1:10">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" s="2">
         <v>6</v>
       </c>
@@ -18256,7 +18243,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="212" spans="1:10" ht="14.5">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B212" s="3" t="s">
         <v>66</v>
       </c>
@@ -18264,7 +18251,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="214" spans="1:10">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
         <v>7</v>
       </c>
@@ -18272,7 +18259,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="215" spans="1:10" ht="14.5">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B215" s="3" t="s">
         <v>69</v>
       </c>
@@ -18280,7 +18267,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="216" spans="1:10" ht="14.5">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B216" s="3" t="s">
         <v>70</v>
       </c>
@@ -18288,7 +18275,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="218" spans="1:10">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
         <v>8</v>
       </c>
@@ -18296,7 +18283,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="220" spans="1:10">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" s="2">
         <v>9</v>
       </c>
@@ -18304,7 +18291,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="238" spans="1:2">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238" s="2">
         <v>10</v>
       </c>
@@ -18312,12 +18299,12 @@
         <v>73</v>
       </c>
     </row>
-    <row r="239" spans="1:2">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B239" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="266" spans="1:13">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A266" s="2">
         <v>11</v>
       </c>
@@ -18325,7 +18312,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="268" spans="1:13">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A268" s="2">
         <v>12</v>
       </c>
@@ -18339,7 +18326,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="279" spans="12:13">
+    <row r="279" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L279" s="2">
         <v>14</v>
       </c>
@@ -18347,7 +18334,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="289" spans="12:13">
+    <row r="289" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L289" s="2">
         <v>15</v>
       </c>
@@ -18355,22 +18342,22 @@
         <v>850</v>
       </c>
     </row>
-    <row r="290" spans="12:13">
+    <row r="290" spans="12:13" x14ac:dyDescent="0.25">
       <c r="M290" s="91"/>
     </row>
-    <row r="291" spans="12:13">
+    <row r="291" spans="12:13" x14ac:dyDescent="0.25">
       <c r="M291" s="91"/>
     </row>
-    <row r="292" spans="12:13">
+    <row r="292" spans="12:13" x14ac:dyDescent="0.25">
       <c r="M292" s="91"/>
     </row>
-    <row r="293" spans="12:13">
+    <row r="293" spans="12:13" x14ac:dyDescent="0.25">
       <c r="M293" s="91"/>
     </row>
-    <row r="294" spans="12:13">
+    <row r="294" spans="12:13" x14ac:dyDescent="0.25">
       <c r="M294" s="91"/>
     </row>
-    <row r="306" spans="12:13" ht="18">
+    <row r="306" spans="12:13" ht="18.75" x14ac:dyDescent="0.4">
       <c r="L306" s="2">
         <v>16</v>
       </c>
@@ -18378,7 +18365,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="316" spans="12:13" ht="18">
+    <row r="316" spans="12:13" ht="18.75" x14ac:dyDescent="0.4">
       <c r="L316" s="2">
         <v>17</v>
       </c>
@@ -18386,7 +18373,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="323" spans="12:13">
+    <row r="323" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L323" s="2">
         <v>18</v>
       </c>
@@ -18394,7 +18381,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="331" spans="12:13">
+    <row r="331" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L331" s="2">
         <v>19</v>
       </c>
@@ -18402,7 +18389,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="339" spans="13:13">
+    <row r="339" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M339" s="2" t="s">
         <v>855</v>
       </c>
@@ -18434,61 +18421,61 @@
     <tabColor theme="0" tint="-0.34998626667073579"/>
   </sheetPr>
   <dimension ref="A1:I97"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="2"/>
-    <col min="2" max="2" width="9.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.7265625" style="2"/>
+    <col min="1" max="1" width="8.7109375" style="2"/>
+    <col min="2" max="2" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.7109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="22.5">
+    <row r="1" spans="1:1" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="67" customHeight="1">
+    <row r="2" spans="1:1" ht="66.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="17.5">
+    <row r="42" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B45" s="5" t="s">
         <v>80</v>
       </c>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B46" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="17.5">
+    <row r="83" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A83" s="8" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
         <v>30</v>
       </c>
@@ -18501,17 +18488,17 @@
       <c r="H85" s="5"/>
       <c r="I85" s="5"/>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="20">
+    <row r="89" spans="1:9" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A89" s="61" t="s">
         <v>85</v>
       </c>
@@ -18522,32 +18509,32 @@
       <c r="F89" s="62"/>
       <c r="G89" s="62"/>
     </row>
-    <row r="91" spans="1:9" ht="17.5">
+    <row r="91" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A91" s="8" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B93" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B94" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B95" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B96" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="97" spans="2:2">
+    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B97" s="2" t="s">
         <v>91</v>
       </c>
@@ -18565,32 +18552,32 @@
     <tabColor theme="0" tint="-0.34998626667073579"/>
   </sheetPr>
   <dimension ref="A1:Q131"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="8.7265625" style="2"/>
+    <col min="1" max="16384" width="8.7109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="22.5">
+    <row r="1" spans="1:1" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="17.5">
+    <row r="2" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:1" ht="17.5">
+    <row r="35" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
         <v>96</v>
       </c>
@@ -18598,17 +18585,17 @@
         <v>97</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B63" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B64" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="14.5">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B65" s="2" t="s">
         <v>100</v>
       </c>
@@ -18621,12 +18608,12 @@
       <c r="P65" s="62"/>
       <c r="Q65" s="62"/>
     </row>
-    <row r="66" spans="1:17">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B66" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="14.5">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B67" s="2" t="s">
         <v>102</v>
       </c>
@@ -18639,17 +18626,17 @@
       <c r="P67" s="62"/>
       <c r="Q67" s="62"/>
     </row>
-    <row r="68" spans="1:17">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B68" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="70" spans="1:17">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
         <v>96</v>
       </c>
@@ -18657,17 +18644,17 @@
         <v>105</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B96" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="97" spans="1:17">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B97" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="20">
+    <row r="98" spans="1:17" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B98" s="2" t="s">
         <v>107</v>
       </c>
@@ -18682,12 +18669,12 @@
       <c r="P98" s="62"/>
       <c r="Q98" s="62"/>
     </row>
-    <row r="99" spans="1:17">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B99" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="20">
+    <row r="100" spans="1:17" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B100" s="2" t="s">
         <v>110</v>
       </c>
@@ -18702,17 +18689,17 @@
       <c r="P100" s="62"/>
       <c r="Q100" s="62"/>
     </row>
-    <row r="101" spans="1:17">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B101" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="103" spans="1:17">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="127" spans="1:2">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" s="12" t="s">
         <v>96</v>
       </c>
@@ -18720,12 +18707,12 @@
         <v>105</v>
       </c>
     </row>
-    <row r="128" spans="1:2">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B128" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="129" spans="2:9" ht="20">
+    <row r="129" spans="2:9" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B129" s="2" t="s">
         <v>114</v>
       </c>
@@ -18739,7 +18726,7 @@
       <c r="H129" s="62"/>
       <c r="I129" s="62"/>
     </row>
-    <row r="131" spans="2:9" ht="20">
+    <row r="131" spans="2:9" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B131" s="2" t="s">
         <v>116</v>
       </c>
@@ -18766,39 +18753,39 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:U66"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="2"/>
-    <col min="2" max="2" width="10.6328125" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="8.7265625" style="2"/>
+    <col min="1" max="1" width="8.7109375" style="2"/>
+    <col min="2" max="2" width="10.5703125" style="2" customWidth="1"/>
+    <col min="3" max="16384" width="8.7109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="22.5">
+    <row r="1" spans="1:1" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="17.5">
+    <row r="2" spans="1:1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="41" spans="1:21" ht="17.5">
+    <row r="41" spans="1:21" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="42" spans="1:21">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B42" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="43" spans="1:21">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B43" s="2" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="1:21" ht="14.5">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
         <v>123</v>
       </c>
@@ -18811,7 +18798,7 @@
       <c r="T44" s="62"/>
       <c r="U44" s="62"/>
     </row>
-    <row r="45" spans="1:21" ht="14.5">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B45" s="2" t="s">
         <v>124</v>
       </c>
@@ -18824,12 +18811,12 @@
       <c r="T45" s="62"/>
       <c r="U45" s="62"/>
     </row>
-    <row r="46" spans="1:21">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B46" s="13" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="47" spans="1:21">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="s">
         <v>126</v>
       </c>
@@ -18837,17 +18824,17 @@
         <v>127</v>
       </c>
     </row>
-    <row r="48" spans="1:21">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="49" spans="2:5">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" s="2" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="50" spans="2:5">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B50" s="2" t="s">
         <v>130</v>
       </c>
@@ -18855,77 +18842,77 @@
         <v>131</v>
       </c>
     </row>
-    <row r="51" spans="2:5">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D51" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="52" spans="2:5">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E52" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="53" spans="2:5">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E53" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="54" spans="2:5">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E54" s="2" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="55" spans="2:5">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D55" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="56" spans="2:5">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E56" s="2" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="57" spans="2:5">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E57" s="2" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="59" spans="2:5">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C59" s="2" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="60" spans="2:5">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D60" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="61" spans="2:5">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E61" s="2" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="62" spans="2:5">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E62" s="2" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="63" spans="2:5">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E63" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="64" spans="2:5">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
       <c r="D64" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="65" spans="5:5">
+    <row r="65" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E65" s="2" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="66" spans="5:5">
+    <row r="66" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E66" s="2" t="s">
         <v>141</v>
       </c>
@@ -18943,14 +18930,14 @@
     <tabColor theme="0" tint="-0.34998626667073579"/>
   </sheetPr>
   <dimension ref="A1:Q24"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="29.15" customHeight="1">
+    <row r="1" spans="1:1" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>96</v>
       </c>
@@ -18960,7 +18947,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="12"/>
       <c r="B19" s="2" t="s">
         <v>145</v>
@@ -18974,7 +18961,7 @@
       <c r="P19" s="63"/>
       <c r="Q19" s="63"/>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="12"/>
       <c r="B20" s="2"/>
       <c r="C20" s="43"/>
@@ -18987,7 +18974,7 @@
       <c r="P20" s="75"/>
       <c r="Q20" s="75"/>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
         <v>146</v>
@@ -18995,7 +18982,7 @@
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="3" t="s">
         <v>147</v>
@@ -19003,7 +18990,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:17">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="3" t="s">
         <v>148</v>
@@ -19011,7 +18998,7 @@
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
     </row>
-    <row r="24" spans="1:17">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="3" t="s">
         <v>149</v>
@@ -19032,14 +19019,14 @@
     <tabColor theme="0" tint="-0.34998626667073579"/>
   </sheetPr>
   <dimension ref="A1:P48"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="22.5">
+    <row r="1" spans="1:1" ht="22.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>96</v>
       </c>
@@ -19048,21 +19035,21 @@
       </c>
       <c r="C20" s="2"/>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="12"/>
       <c r="B21" s="2" t="s">
         <v>151</v>
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="12"/>
       <c r="B22" s="2" t="s">
         <v>152</v>
       </c>
       <c r="C22" s="43"/>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="12"/>
       <c r="B23" s="2" t="s">
         <v>153</v>
@@ -19072,7 +19059,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2" t="s">
         <v>154</v>
@@ -19086,7 +19073,7 @@
       <c r="O24" s="63"/>
       <c r="P24" s="63"/>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="57" t="s">
         <v>155</v>
@@ -19094,22 +19081,22 @@
       <c r="C25" s="6"/>
       <c r="D25" s="58"/>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="3"/>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
     </row>
-    <row r="46" spans="2:14">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B46" s="55" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="47" spans="2:14">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B47" s="59" t="s">
         <v>157</v>
       </c>
@@ -19126,7 +19113,7 @@
       <c r="M47" s="60"/>
       <c r="N47" s="60"/>
     </row>
-    <row r="48" spans="2:14">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
         <v>158</v>
       </c>
@@ -19147,54 +19134,54 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:AE215"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="8.7265625" style="2"/>
-    <col min="3" max="4" width="15.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="11" width="8.7265625" style="2"/>
-    <col min="12" max="12" width="5.36328125" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="8.7265625" style="2"/>
+    <col min="1" max="2" width="8.7109375" style="2"/>
+    <col min="3" max="4" width="15.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="11" width="8.7109375" style="2"/>
+    <col min="12" max="12" width="5.42578125" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="8.7109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="67" customFormat="1" ht="20">
+    <row r="1" spans="1:1" s="67" customFormat="1" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A1" s="66" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" s="67" customFormat="1">
+    <row r="2" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="68" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="3" spans="1:1" s="67" customFormat="1"/>
-    <row r="4" spans="1:1" s="47" customFormat="1"/>
-    <row r="5" spans="1:1" s="47" customFormat="1"/>
-    <row r="6" spans="1:1" s="47" customFormat="1"/>
-    <row r="7" spans="1:1" s="47" customFormat="1"/>
-    <row r="8" spans="1:1" s="47" customFormat="1"/>
-    <row r="9" spans="1:1" s="47" customFormat="1"/>
-    <row r="10" spans="1:1" s="47" customFormat="1"/>
-    <row r="11" spans="1:1" s="47" customFormat="1"/>
-    <row r="12" spans="1:1" s="47" customFormat="1"/>
-    <row r="13" spans="1:1" s="47" customFormat="1"/>
-    <row r="14" spans="1:1" s="47" customFormat="1"/>
-    <row r="15" spans="1:1" s="47" customFormat="1"/>
-    <row r="16" spans="1:1" s="47" customFormat="1"/>
-    <row r="17" spans="1:2" s="47" customFormat="1"/>
-    <row r="18" spans="1:2" s="47" customFormat="1"/>
-    <row r="19" spans="1:2" s="47" customFormat="1"/>
-    <row r="20" spans="1:2" s="67" customFormat="1"/>
-    <row r="21" spans="1:2" s="67" customFormat="1"/>
-    <row r="22" spans="1:2" s="67" customFormat="1"/>
-    <row r="23" spans="1:2" s="67" customFormat="1"/>
-    <row r="24" spans="1:2" s="67" customFormat="1"/>
-    <row r="25" spans="1:2" s="67" customFormat="1"/>
-    <row r="26" spans="1:2" s="67" customFormat="1"/>
-    <row r="27" spans="1:2" s="67" customFormat="1"/>
-    <row r="28" spans="1:2" s="67" customFormat="1"/>
-    <row r="29" spans="1:2" s="67" customFormat="1"/>
-    <row r="30" spans="1:2" s="67" customFormat="1"/>
-    <row r="31" spans="1:2" s="67" customFormat="1">
+    <row r="3" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:1" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:2" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="1:2" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:2" s="47" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:2" s="67" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:2" s="67" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:2" s="67" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:2" s="67" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:2" s="67" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:2" s="67" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:2" s="67" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:2" s="67" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:2" s="67" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:2" s="67" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:2" s="67" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:2" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="69" t="s">
         <v>96</v>
       </c>
@@ -19202,25 +19189,25 @@
         <v>160</v>
       </c>
     </row>
-    <row r="32" spans="1:2" s="67" customFormat="1">
+    <row r="32" spans="1:2" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="69"/>
       <c r="B32" s="67" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="33" spans="1:11" s="67" customFormat="1">
+    <row r="33" spans="1:11" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="69"/>
       <c r="C33" s="70" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="34" spans="1:11" s="67" customFormat="1">
+    <row r="34" spans="1:11" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="69"/>
       <c r="C34" s="70" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="35" spans="1:11" s="67" customFormat="1">
+    <row r="35" spans="1:11" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="69"/>
       <c r="B35" s="6" t="s">
         <v>164</v>
@@ -19235,7 +19222,7 @@
       <c r="J35" s="6"/>
       <c r="K35" s="6"/>
     </row>
-    <row r="36" spans="1:11" s="67" customFormat="1">
+    <row r="36" spans="1:11" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="69"/>
       <c r="B36" s="6" t="s">
         <v>165</v>
@@ -19250,29 +19237,29 @@
       <c r="J36" s="6"/>
       <c r="K36" s="6"/>
     </row>
-    <row r="37" spans="1:11" s="67" customFormat="1">
+    <row r="37" spans="1:11" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="69"/>
       <c r="C37" s="70"/>
     </row>
-    <row r="38" spans="1:11" s="67" customFormat="1">
+    <row r="38" spans="1:11" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="69"/>
       <c r="C38" s="70"/>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C67" s="3"/>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>167</v>
       </c>
       <c r="C68" s="3"/>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B69" s="2" t="s">
         <v>168</v>
       </c>
@@ -19281,165 +19268,165 @@
         <v>169</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="14.5">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B70" s="14"/>
       <c r="C70" s="3"/>
       <c r="D70" s="2" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C71" s="3"/>
       <c r="D71" s="2" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B72" s="2" t="s">
         <v>172</v>
       </c>
       <c r="C72" s="3"/>
     </row>
-    <row r="73" spans="1:11" ht="14.5">
-      <c r="C73" s="93" t="s">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C73" s="94" t="s">
         <v>173</v>
       </c>
-      <c r="D73" s="93"/>
-      <c r="J73" s="94" t="s">
+      <c r="D73" s="94"/>
+      <c r="J73" s="95" t="s">
         <v>174</v>
       </c>
-      <c r="K73" s="94"/>
-    </row>
-    <row r="74" spans="1:11">
+      <c r="K73" s="95"/>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C74" s="3"/>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C75" s="3"/>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C76" s="3"/>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C77" s="3"/>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C78" s="3"/>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C79" s="3"/>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C80" s="3"/>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C81" s="3"/>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C82" s="3"/>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C83" s="3"/>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C84" s="3"/>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C85" s="3"/>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C86" s="3"/>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C87" s="3"/>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C88" s="3"/>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C89" s="3"/>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C90" s="3"/>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C91" s="3"/>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C92" s="3"/>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C93" s="3"/>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C94" s="3"/>
     </row>
-    <row r="95" spans="1:3" s="6" customFormat="1" ht="17.5">
+    <row r="95" spans="1:3" s="6" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A95" s="92" t="s">
         <v>175</v>
       </c>
       <c r="C95" s="57"/>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B96" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C96" s="3"/>
     </row>
-    <row r="97" spans="2:14">
+    <row r="97" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C97" s="3" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="98" spans="2:14">
+    <row r="98" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C98" s="3" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="99" spans="2:14">
+    <row r="99" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B99" s="2" t="s">
         <v>179</v>
       </c>
       <c r="C99" s="3"/>
     </row>
-    <row r="100" spans="2:14" ht="14.5">
+    <row r="100" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C100" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D100" s="93" t="s">
+      <c r="D100" s="94" t="s">
         <v>173</v>
       </c>
-      <c r="E100" s="93"/>
-    </row>
-    <row r="101" spans="2:14">
+      <c r="E100" s="94"/>
+    </row>
+    <row r="101" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C101" s="3" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="102" spans="2:14">
+    <row r="102" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C102" s="3"/>
     </row>
-    <row r="103" spans="2:14">
+    <row r="103" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C103" s="3"/>
     </row>
-    <row r="104" spans="2:14">
+    <row r="104" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C104" s="3"/>
     </row>
-    <row r="106" spans="2:14">
+    <row r="106" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C106" s="3" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="107" spans="2:14">
+    <row r="107" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B107" s="2" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="108" spans="2:14">
+    <row r="108" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C108" s="3" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="109" spans="2:14" ht="14.5">
+    <row r="109" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C109" s="3" t="s">
         <v>185</v>
       </c>
@@ -19451,21 +19438,21 @@
         <v>187</v>
       </c>
     </row>
-    <row r="110" spans="2:14">
+    <row r="110" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C110" s="3" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="111" spans="2:14">
+    <row r="111" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C111" s="3" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="120" spans="3:4" ht="13.5" customHeight="1"/>
-    <row r="121" spans="3:4" ht="13.5" customHeight="1"/>
-    <row r="122" spans="3:4" ht="13.5" customHeight="1"/>
-    <row r="123" spans="3:4" ht="13.5" customHeight="1"/>
-    <row r="124" spans="3:4" ht="13.5" customHeight="1">
+    <row r="120" spans="3:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="3:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="3:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="3:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="3:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C124" s="3" t="s">
         <v>180</v>
       </c>
@@ -19473,78 +19460,78 @@
         <v>174</v>
       </c>
     </row>
-    <row r="125" spans="3:4" ht="13.5" customHeight="1">
+    <row r="125" spans="3:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C125" s="3" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="126" spans="3:4" ht="13.5" customHeight="1">
+    <row r="126" spans="3:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C126" s="3" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="127" spans="3:4" ht="13.5" customHeight="1">
+    <row r="127" spans="3:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C127" s="3" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="128" spans="3:4" ht="13.5" customHeight="1"/>
-    <row r="129" spans="1:17" ht="13.5" customHeight="1"/>
-    <row r="130" spans="1:17" ht="13.5" customHeight="1"/>
-    <row r="131" spans="1:17" ht="13.5" customHeight="1"/>
-    <row r="132" spans="1:17" ht="13.5" customHeight="1"/>
-    <row r="133" spans="1:17" ht="13.5" customHeight="1"/>
-    <row r="134" spans="1:17" ht="13.5" customHeight="1"/>
-    <row r="135" spans="1:17" ht="13.5" customHeight="1"/>
-    <row r="136" spans="1:17">
+    <row r="128" spans="3:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B136" s="2" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="137" spans="1:17">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B137" s="2" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="138" spans="1:17">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C138" s="2" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="139" spans="1:17" ht="14.5">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C139" s="14" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="140" spans="1:17" ht="13.5" customHeight="1"/>
-    <row r="141" spans="1:17" ht="13.5" customHeight="1">
+    <row r="140" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="143" spans="1:17" ht="13.5" customHeight="1"/>
-    <row r="144" spans="1:17" ht="22" customHeight="1">
-      <c r="A144" s="95" t="s">
+    <row r="143" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="96" t="s">
         <v>198</v>
       </c>
-      <c r="B144" s="95"/>
-      <c r="C144" s="95"/>
-      <c r="D144" s="95"/>
-      <c r="E144" s="95"/>
-      <c r="F144" s="95"/>
-      <c r="G144" s="95"/>
-      <c r="H144" s="95"/>
-      <c r="I144" s="95"/>
-      <c r="J144" s="95"/>
-      <c r="K144" s="95"/>
-      <c r="L144" s="95"/>
-      <c r="M144" s="95"/>
-      <c r="N144" s="95"/>
-      <c r="O144" s="95"/>
-      <c r="P144" s="95"/>
-      <c r="Q144" s="95"/>
-    </row>
-    <row r="145" spans="1:17" ht="13.5" customHeight="1">
+      <c r="B144" s="96"/>
+      <c r="C144" s="96"/>
+      <c r="D144" s="96"/>
+      <c r="E144" s="96"/>
+      <c r="F144" s="96"/>
+      <c r="G144" s="96"/>
+      <c r="H144" s="96"/>
+      <c r="I144" s="96"/>
+      <c r="J144" s="96"/>
+      <c r="K144" s="96"/>
+      <c r="L144" s="96"/>
+      <c r="M144" s="96"/>
+      <c r="N144" s="96"/>
+      <c r="O144" s="96"/>
+      <c r="P144" s="96"/>
+      <c r="Q144" s="96"/>
+    </row>
+    <row r="145" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="59" t="s">
         <v>866</v>
       </c>
@@ -19565,16 +19552,16 @@
       <c r="P145" s="59"/>
       <c r="Q145" s="59"/>
     </row>
-    <row r="146" spans="1:17" ht="19" customHeight="1">
-      <c r="A146" s="95" t="s">
+    <row r="146" spans="1:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="96" t="s">
         <v>861</v>
       </c>
-      <c r="B146" s="95"/>
-      <c r="C146" s="95"/>
-      <c r="D146" s="95"/>
-      <c r="E146" s="95"/>
-      <c r="F146" s="95"/>
-      <c r="G146" s="95"/>
+      <c r="B146" s="96"/>
+      <c r="C146" s="96"/>
+      <c r="D146" s="96"/>
+      <c r="E146" s="96"/>
+      <c r="F146" s="96"/>
+      <c r="G146" s="96"/>
       <c r="H146" s="59"/>
       <c r="I146" s="59"/>
       <c r="J146" s="59"/>
@@ -19586,16 +19573,16 @@
       <c r="P146" s="59"/>
       <c r="Q146" s="59"/>
     </row>
-    <row r="147" spans="1:17" ht="19" customHeight="1">
+    <row r="147" spans="1:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="59" t="s">
         <v>856</v>
       </c>
-      <c r="B147" s="96"/>
-      <c r="C147" s="96"/>
-      <c r="D147" s="96"/>
-      <c r="E147" s="96"/>
-      <c r="F147" s="96"/>
-      <c r="G147" s="96"/>
+      <c r="B147" s="93"/>
+      <c r="C147" s="93"/>
+      <c r="D147" s="93"/>
+      <c r="E147" s="93"/>
+      <c r="F147" s="93"/>
+      <c r="G147" s="93"/>
       <c r="H147" s="59"/>
       <c r="I147" s="59"/>
       <c r="J147" s="59"/>
@@ -19607,37 +19594,37 @@
       <c r="P147" s="59"/>
       <c r="Q147" s="59"/>
     </row>
-    <row r="148" spans="1:17" ht="19" customHeight="1">
-      <c r="A148" s="95" t="s">
+    <row r="148" spans="1:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="96" t="s">
         <v>199</v>
       </c>
-      <c r="B148" s="95"/>
-      <c r="C148" s="95"/>
-      <c r="D148" s="95"/>
-      <c r="E148" s="95"/>
-      <c r="F148" s="95"/>
-      <c r="G148" s="95"/>
-      <c r="H148" s="95"/>
-      <c r="I148" s="95"/>
-      <c r="J148" s="95"/>
-      <c r="K148" s="95"/>
-      <c r="L148" s="95"/>
-      <c r="M148" s="95"/>
-      <c r="N148" s="95"/>
-      <c r="O148" s="95"/>
+      <c r="B148" s="96"/>
+      <c r="C148" s="96"/>
+      <c r="D148" s="96"/>
+      <c r="E148" s="96"/>
+      <c r="F148" s="96"/>
+      <c r="G148" s="96"/>
+      <c r="H148" s="96"/>
+      <c r="I148" s="96"/>
+      <c r="J148" s="96"/>
+      <c r="K148" s="96"/>
+      <c r="L148" s="96"/>
+      <c r="M148" s="96"/>
+      <c r="N148" s="96"/>
+      <c r="O148" s="96"/>
       <c r="P148" s="59"/>
       <c r="Q148" s="59"/>
     </row>
-    <row r="149" spans="1:17" ht="19" customHeight="1">
+    <row r="149" spans="1:17" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="59" t="s">
         <v>866</v>
       </c>
-      <c r="B149" s="96"/>
-      <c r="C149" s="96"/>
-      <c r="D149" s="96"/>
-      <c r="E149" s="96"/>
-      <c r="F149" s="96"/>
-      <c r="G149" s="96"/>
+      <c r="B149" s="93"/>
+      <c r="C149" s="93"/>
+      <c r="D149" s="93"/>
+      <c r="E149" s="93"/>
+      <c r="F149" s="93"/>
+      <c r="G149" s="93"/>
       <c r="H149" s="59"/>
       <c r="I149" s="59"/>
       <c r="J149" s="59"/>
@@ -19649,60 +19636,60 @@
       <c r="P149" s="59"/>
       <c r="Q149" s="59"/>
     </row>
-    <row r="150" spans="1:17" ht="17.5">
-      <c r="A150" s="98" t="s">
+    <row r="150" spans="1:17" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A150" s="96" t="s">
         <v>863</v>
       </c>
-      <c r="B150" s="98"/>
-      <c r="C150" s="98"/>
-      <c r="D150" s="98"/>
-      <c r="E150" s="98"/>
-      <c r="F150" s="98"/>
-      <c r="G150" s="98"/>
-      <c r="H150" s="98"/>
-      <c r="I150" s="98"/>
-      <c r="J150" s="98"/>
-      <c r="K150" s="98"/>
-      <c r="L150" s="98"/>
-      <c r="M150" s="98"/>
-      <c r="N150" s="98"/>
-      <c r="O150" s="98"/>
-      <c r="P150" s="98"/>
-      <c r="Q150" s="98"/>
-    </row>
-    <row r="151" spans="1:17" ht="17.5">
-      <c r="A151" s="99" t="s">
+      <c r="B150" s="96"/>
+      <c r="C150" s="96"/>
+      <c r="D150" s="96"/>
+      <c r="E150" s="96"/>
+      <c r="F150" s="96"/>
+      <c r="G150" s="96"/>
+      <c r="H150" s="96"/>
+      <c r="I150" s="96"/>
+      <c r="J150" s="96"/>
+      <c r="K150" s="96"/>
+      <c r="L150" s="96"/>
+      <c r="M150" s="96"/>
+      <c r="N150" s="96"/>
+      <c r="O150" s="96"/>
+      <c r="P150" s="96"/>
+      <c r="Q150" s="96"/>
+    </row>
+    <row r="151" spans="1:17" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A151" s="59" t="s">
         <v>856</v>
       </c>
-      <c r="B151" s="100"/>
-      <c r="C151" s="100"/>
-      <c r="D151" s="100"/>
-      <c r="E151" s="100"/>
-      <c r="F151" s="100"/>
-      <c r="G151" s="100"/>
-      <c r="H151" s="99"/>
-      <c r="I151" s="99"/>
-      <c r="J151" s="99"/>
-      <c r="K151" s="99"/>
-      <c r="L151" s="99"/>
-      <c r="M151" s="99"/>
-      <c r="N151" s="99"/>
-      <c r="O151" s="99"/>
-      <c r="P151" s="99"/>
-      <c r="Q151" s="100"/>
-    </row>
-    <row r="152" spans="1:17" ht="17.5" customHeight="1">
-      <c r="A152" s="95" t="s">
+      <c r="B151" s="93"/>
+      <c r="C151" s="93"/>
+      <c r="D151" s="93"/>
+      <c r="E151" s="93"/>
+      <c r="F151" s="93"/>
+      <c r="G151" s="93"/>
+      <c r="H151" s="59"/>
+      <c r="I151" s="59"/>
+      <c r="J151" s="59"/>
+      <c r="K151" s="59"/>
+      <c r="L151" s="59"/>
+      <c r="M151" s="59"/>
+      <c r="N151" s="59"/>
+      <c r="O151" s="59"/>
+      <c r="P151" s="59"/>
+      <c r="Q151" s="93"/>
+    </row>
+    <row r="152" spans="1:17" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="96" t="s">
         <v>200</v>
       </c>
-      <c r="B152" s="95"/>
-      <c r="C152" s="95"/>
-      <c r="D152" s="95"/>
-      <c r="E152" s="95"/>
-      <c r="F152" s="95"/>
-      <c r="G152" s="95"/>
-    </row>
-    <row r="153" spans="1:17">
+      <c r="B152" s="96"/>
+      <c r="C152" s="96"/>
+      <c r="D152" s="96"/>
+      <c r="E152" s="96"/>
+      <c r="F152" s="96"/>
+      <c r="G152" s="96"/>
+    </row>
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153" s="59" t="s">
         <v>865</v>
       </c>
@@ -19713,16 +19700,16 @@
       <c r="F153" s="59"/>
       <c r="G153" s="59"/>
     </row>
-    <row r="154" spans="1:17" ht="17.5">
-      <c r="A154" s="98" t="s">
+    <row r="154" spans="1:17" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A154" s="96" t="s">
         <v>201</v>
       </c>
-      <c r="B154" s="98"/>
-      <c r="C154" s="98"/>
-      <c r="D154" s="98"/>
-      <c r="E154" s="98"/>
-      <c r="F154" s="98"/>
-      <c r="G154" s="98"/>
+      <c r="B154" s="96"/>
+      <c r="C154" s="96"/>
+      <c r="D154" s="96"/>
+      <c r="E154" s="96"/>
+      <c r="F154" s="96"/>
+      <c r="G154" s="96"/>
       <c r="J154" s="59" t="s">
         <v>859</v>
       </c>
@@ -19734,29 +19721,29 @@
       <c r="P154" s="59"/>
       <c r="Q154" s="59"/>
     </row>
-    <row r="155" spans="1:17">
-      <c r="A155" s="99" t="s">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A155" s="59" t="s">
         <v>865</v>
       </c>
-      <c r="B155" s="99"/>
-      <c r="C155" s="99"/>
-      <c r="D155" s="99"/>
-      <c r="E155" s="99"/>
-      <c r="F155" s="99"/>
-      <c r="G155" s="99"/>
-    </row>
-    <row r="156" spans="1:17" ht="17.5">
-      <c r="A156" s="95" t="s">
+      <c r="B155" s="59"/>
+      <c r="C155" s="59"/>
+      <c r="D155" s="59"/>
+      <c r="E155" s="59"/>
+      <c r="F155" s="59"/>
+      <c r="G155" s="59"/>
+    </row>
+    <row r="156" spans="1:17" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A156" s="96" t="s">
         <v>202</v>
       </c>
-      <c r="B156" s="95"/>
-      <c r="C156" s="95"/>
-      <c r="D156" s="95"/>
-      <c r="E156" s="95"/>
-      <c r="F156" s="95"/>
-      <c r="G156" s="95"/>
-    </row>
-    <row r="157" spans="1:17">
+      <c r="B156" s="96"/>
+      <c r="C156" s="96"/>
+      <c r="D156" s="96"/>
+      <c r="E156" s="96"/>
+      <c r="F156" s="96"/>
+      <c r="G156" s="96"/>
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157" s="59" t="s">
         <v>866</v>
       </c>
@@ -19767,7 +19754,7 @@
       <c r="F157" s="59"/>
       <c r="G157" s="59"/>
     </row>
-    <row r="158" spans="1:17" ht="15">
+    <row r="158" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" s="97" t="s">
         <v>203</v>
       </c>
@@ -19778,7 +19765,7 @@
       <c r="F158" s="97"/>
       <c r="G158" s="97"/>
     </row>
-    <row r="159" spans="1:17">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159" s="59" t="s">
         <v>866</v>
       </c>
@@ -19789,46 +19776,46 @@
       <c r="F159" s="59"/>
       <c r="G159" s="59"/>
     </row>
-    <row r="161" spans="1:31" ht="17.5">
-      <c r="A161" s="98" t="s">
+    <row r="161" spans="1:31" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A161" s="96" t="s">
         <v>204</v>
       </c>
-      <c r="B161" s="98"/>
-      <c r="C161" s="98"/>
-      <c r="D161" s="98"/>
-      <c r="E161" s="98"/>
-      <c r="F161" s="98"/>
-      <c r="G161" s="98"/>
-      <c r="H161" s="98"/>
-      <c r="I161" s="98"/>
-      <c r="J161" s="98"/>
-    </row>
-    <row r="162" spans="1:31">
-      <c r="A162" s="99" t="s">
+      <c r="B161" s="96"/>
+      <c r="C161" s="96"/>
+      <c r="D161" s="96"/>
+      <c r="E161" s="96"/>
+      <c r="F161" s="96"/>
+      <c r="G161" s="96"/>
+      <c r="H161" s="96"/>
+      <c r="I161" s="96"/>
+      <c r="J161" s="96"/>
+    </row>
+    <row r="162" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A162" s="59" t="s">
         <v>857</v>
       </c>
-      <c r="B162" s="99"/>
-      <c r="C162" s="99"/>
-      <c r="D162" s="99"/>
-      <c r="E162" s="99"/>
-      <c r="F162" s="99"/>
-      <c r="G162" s="99"/>
-      <c r="H162" s="99"/>
-      <c r="I162" s="99"/>
-      <c r="J162" s="99"/>
-    </row>
-    <row r="163" spans="1:31" ht="17.5">
-      <c r="A163" s="95" t="s">
+      <c r="B162" s="59"/>
+      <c r="C162" s="59"/>
+      <c r="D162" s="59"/>
+      <c r="E162" s="59"/>
+      <c r="F162" s="59"/>
+      <c r="G162" s="59"/>
+      <c r="H162" s="59"/>
+      <c r="I162" s="59"/>
+      <c r="J162" s="59"/>
+    </row>
+    <row r="163" spans="1:31" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A163" s="96" t="s">
         <v>205</v>
       </c>
-      <c r="B163" s="95"/>
-      <c r="C163" s="95"/>
-      <c r="D163" s="95"/>
-      <c r="E163" s="95"/>
-      <c r="F163" s="95"/>
-      <c r="G163" s="95"/>
-    </row>
-    <row r="164" spans="1:31">
+      <c r="B163" s="96"/>
+      <c r="C163" s="96"/>
+      <c r="D163" s="96"/>
+      <c r="E163" s="96"/>
+      <c r="F163" s="96"/>
+      <c r="G163" s="96"/>
+    </row>
+    <row r="164" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A164" s="59"/>
       <c r="B164" s="59"/>
       <c r="C164" s="59"/>
@@ -19837,18 +19824,18 @@
       <c r="F164" s="59"/>
       <c r="G164" s="59"/>
     </row>
-    <row r="165" spans="1:31" ht="17.5">
-      <c r="A165" s="95" t="s">
+    <row r="165" spans="1:31" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A165" s="96" t="s">
         <v>206</v>
       </c>
-      <c r="B165" s="95"/>
-      <c r="C165" s="95"/>
-      <c r="D165" s="95"/>
-      <c r="E165" s="95"/>
-      <c r="F165" s="95"/>
-      <c r="G165" s="95"/>
-    </row>
-    <row r="166" spans="1:31">
+      <c r="B165" s="96"/>
+      <c r="C165" s="96"/>
+      <c r="D165" s="96"/>
+      <c r="E165" s="96"/>
+      <c r="F165" s="96"/>
+      <c r="G165" s="96"/>
+    </row>
+    <row r="166" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A166" s="59"/>
       <c r="B166" s="59"/>
       <c r="C166" s="59"/>
@@ -19857,16 +19844,16 @@
       <c r="F166" s="59"/>
       <c r="G166" s="59"/>
     </row>
-    <row r="167" spans="1:31" s="67" customFormat="1" ht="17.5">
-      <c r="A167" s="95" t="s">
+    <row r="167" spans="1:31" s="67" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A167" s="96" t="s">
         <v>862</v>
       </c>
-      <c r="B167" s="95"/>
-      <c r="C167" s="95"/>
-      <c r="D167" s="95"/>
-      <c r="E167" s="95"/>
-      <c r="F167" s="95"/>
-      <c r="G167" s="95"/>
+      <c r="B167" s="96"/>
+      <c r="C167" s="96"/>
+      <c r="D167" s="96"/>
+      <c r="E167" s="96"/>
+      <c r="F167" s="96"/>
+      <c r="G167" s="96"/>
       <c r="H167" s="2"/>
       <c r="I167" s="2"/>
       <c r="J167" s="2"/>
@@ -19892,7 +19879,7 @@
       <c r="AD167" s="2"/>
       <c r="AE167" s="2"/>
     </row>
-    <row r="168" spans="1:31">
+    <row r="168" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A168" s="59" t="s">
         <v>860</v>
       </c>
@@ -19903,45 +19890,45 @@
       <c r="F168" s="59"/>
       <c r="G168" s="59"/>
     </row>
-    <row r="169" spans="1:31" ht="17.5">
-      <c r="A169" s="98" t="s">
+    <row r="169" spans="1:31" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A169" s="96" t="s">
         <v>207</v>
       </c>
-      <c r="B169" s="98"/>
-      <c r="C169" s="98"/>
-      <c r="D169" s="98"/>
-      <c r="E169" s="98"/>
-      <c r="F169" s="98"/>
-      <c r="G169" s="98"/>
-    </row>
-    <row r="170" spans="1:31">
-      <c r="A170" s="99" t="s">
+      <c r="B169" s="96"/>
+      <c r="C169" s="96"/>
+      <c r="D169" s="96"/>
+      <c r="E169" s="96"/>
+      <c r="F169" s="96"/>
+      <c r="G169" s="96"/>
+    </row>
+    <row r="170" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A170" s="59" t="s">
         <v>858</v>
       </c>
-      <c r="B170" s="99"/>
-      <c r="C170" s="99"/>
-      <c r="D170" s="99"/>
-      <c r="E170" s="99"/>
-      <c r="F170" s="99"/>
-      <c r="G170" s="99"/>
-    </row>
-    <row r="172" spans="1:31" ht="17.5">
-      <c r="A172" s="101" t="s">
+      <c r="B170" s="59"/>
+      <c r="C170" s="59"/>
+      <c r="D170" s="59"/>
+      <c r="E170" s="59"/>
+      <c r="F170" s="59"/>
+      <c r="G170" s="59"/>
+    </row>
+    <row r="172" spans="1:31" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A172" s="98" t="s">
         <v>175</v>
       </c>
-      <c r="B172" s="99"/>
-      <c r="C172" s="102"/>
-      <c r="D172" s="99"/>
-    </row>
-    <row r="173" spans="1:31">
-      <c r="A173" s="99" t="s">
+      <c r="B172" s="59"/>
+      <c r="C172" s="99"/>
+      <c r="D172" s="59"/>
+    </row>
+    <row r="173" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A173" s="59" t="s">
         <v>864</v>
       </c>
-      <c r="B173" s="99"/>
-      <c r="C173" s="99"/>
-      <c r="D173" s="99"/>
-    </row>
-    <row r="174" spans="1:31" ht="20.149999999999999" customHeight="1">
+      <c r="B173" s="59"/>
+      <c r="C173" s="59"/>
+      <c r="D173" s="59"/>
+    </row>
+    <row r="174" spans="1:31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="76" t="s">
         <v>208</v>
       </c>
@@ -19950,7 +19937,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="175" spans="1:31" ht="17.5" customHeight="1">
+    <row r="175" spans="1:31" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="76" t="s">
         <v>210</v>
       </c>
@@ -19959,73 +19946,73 @@
         <v>209</v>
       </c>
     </row>
-    <row r="176" spans="1:31" ht="17.5">
+    <row r="176" spans="1:31" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A176" s="39"/>
     </row>
-    <row r="177" spans="2:3">
+    <row r="177" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B177" s="2" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="178" spans="2:3">
+    <row r="178" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B178" s="2" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="179" spans="2:3">
+    <row r="179" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C179" s="2" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="180" spans="2:3">
+    <row r="180" spans="2:3" x14ac:dyDescent="0.25">
       <c r="C180" s="2" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="186" spans="2:3">
+    <row r="186" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B186" s="12"/>
     </row>
-    <row r="193" spans="1:20">
+    <row r="193" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B193" s="54" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="195" spans="1:20" ht="20">
+    <row r="195" spans="1:20" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A195" s="9" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="196" spans="1:20">
+    <row r="196" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B196" s="2" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="197" spans="1:20">
+    <row r="197" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B197" s="2" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="198" spans="1:20">
+    <row r="198" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B198" s="2" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="199" spans="1:20">
+    <row r="199" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B199" s="77" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="200" spans="1:20">
+    <row r="200" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C200" s="4" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="202" spans="1:20">
+    <row r="202" spans="1:20" x14ac:dyDescent="0.25">
       <c r="F202" s="3" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="203" spans="1:20">
+    <row r="203" spans="1:20" x14ac:dyDescent="0.25">
       <c r="F203" s="6" t="s">
         <v>222</v>
       </c>
@@ -20045,12 +20032,12 @@
       <c r="S203" s="67"/>
       <c r="T203" s="67"/>
     </row>
-    <row r="204" spans="1:20">
+    <row r="204" spans="1:20" x14ac:dyDescent="0.25">
       <c r="F204" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="205" spans="1:20">
+    <row r="205" spans="1:20" x14ac:dyDescent="0.25">
       <c r="F205" s="6" t="s">
         <v>225</v>
       </c>
@@ -20070,26 +20057,26 @@
       <c r="S205" s="67"/>
       <c r="T205" s="67"/>
     </row>
-    <row r="206" spans="1:20">
+    <row r="206" spans="1:20" x14ac:dyDescent="0.25">
       <c r="F206" s="3"/>
     </row>
-    <row r="209" spans="2:16">
+    <row r="209" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B209" s="55" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="211" spans="2:16">
+    <row r="211" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C211" s="5" t="s">
         <v>228</v>
       </c>
       <c r="D211" s="6"/>
     </row>
-    <row r="212" spans="2:16">
+    <row r="212" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C212" s="2" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="213" spans="2:16">
+    <row r="213" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C213" s="2" t="s">
         <v>230</v>
       </c>
@@ -20099,18 +20086,27 @@
       <c r="O213" s="62"/>
       <c r="P213" s="62"/>
     </row>
-    <row r="214" spans="2:16">
+    <row r="214" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C214" s="2" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="215" spans="2:16" ht="14.5">
+    <row r="215" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B215" s="14" t="s">
         <v>231</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A165:G165"/>
+    <mergeCell ref="A167:G167"/>
+    <mergeCell ref="A169:G169"/>
+    <mergeCell ref="A163:G163"/>
+    <mergeCell ref="A154:G154"/>
+    <mergeCell ref="A148:O148"/>
+    <mergeCell ref="A156:G156"/>
+    <mergeCell ref="A158:G158"/>
+    <mergeCell ref="A161:J161"/>
     <mergeCell ref="C73:D73"/>
     <mergeCell ref="J73:K73"/>
     <mergeCell ref="D100:E100"/>
@@ -20118,15 +20114,6 @@
     <mergeCell ref="A152:G152"/>
     <mergeCell ref="A150:Q150"/>
     <mergeCell ref="A144:Q144"/>
-    <mergeCell ref="A154:G154"/>
-    <mergeCell ref="A148:O148"/>
-    <mergeCell ref="A156:G156"/>
-    <mergeCell ref="A158:G158"/>
-    <mergeCell ref="A161:J161"/>
-    <mergeCell ref="A165:G165"/>
-    <mergeCell ref="A167:G167"/>
-    <mergeCell ref="A169:G169"/>
-    <mergeCell ref="A163:G163"/>
   </mergeCells>
   <phoneticPr fontId="11"/>
   <hyperlinks>
@@ -20149,21 +20136,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E051964-B2F1-46E4-8090-DFC16253CFF8}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:I244"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.36328125" style="33" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.7265625" style="30" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.6328125" style="34" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" style="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" style="30" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.5703125" style="34" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" style="30" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.6328125" style="34" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.26953125" style="30" customWidth="1"/>
+    <col min="5" max="5" width="32.5703125" style="34" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" style="30" customWidth="1"/>
     <col min="7" max="7" width="9" style="30" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="33"/>
-    <col min="9" max="9" width="41.26953125" style="30" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="41.28515625" style="30" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="21" customFormat="1" ht="11.5">
+    <row r="1" spans="1:9" s="21" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>232</v>
       </c>
@@ -20192,7 +20179,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="21" customFormat="1" ht="0.75" customHeight="1">
+    <row r="2" spans="1:9" s="21" customFormat="1" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="22"/>
       <c r="B2" s="23"/>
       <c r="C2" s="24"/>
@@ -20212,7 +20199,7 @@
       </c>
       <c r="I2" s="23"/>
     </row>
-    <row r="3" spans="1:9" s="21" customFormat="1">
+    <row r="3" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="26">
         <v>7001065118</v>
       </c>
@@ -20239,7 +20226,7 @@
       </c>
       <c r="I3" s="27"/>
     </row>
-    <row r="4" spans="1:9" s="21" customFormat="1">
+    <row r="4" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26">
         <v>7001075118</v>
       </c>
@@ -20266,7 +20253,7 @@
       </c>
       <c r="I4" s="27"/>
     </row>
-    <row r="5" spans="1:9" s="21" customFormat="1">
+    <row r="5" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
         <v>244</v>
       </c>
@@ -20287,7 +20274,7 @@
       <c r="H5" s="29"/>
       <c r="I5" s="27"/>
     </row>
-    <row r="6" spans="1:9" s="21" customFormat="1">
+    <row r="6" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="26">
         <v>5001016131</v>
       </c>
@@ -20312,7 +20299,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="7" spans="1:9" s="21" customFormat="1">
+    <row r="7" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26">
         <v>5001016134</v>
       </c>
@@ -20341,7 +20328,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="8" spans="1:9" s="21" customFormat="1">
+    <row r="8" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="26">
         <v>5001016135</v>
       </c>
@@ -20368,7 +20355,7 @@
       </c>
       <c r="I8" s="27"/>
     </row>
-    <row r="9" spans="1:9" s="21" customFormat="1">
+    <row r="9" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="26">
         <v>5001016136</v>
       </c>
@@ -20395,7 +20382,7 @@
       </c>
       <c r="I9" s="27"/>
     </row>
-    <row r="10" spans="1:9" s="21" customFormat="1">
+    <row r="10" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="26">
         <v>5001016142</v>
       </c>
@@ -20422,7 +20409,7 @@
       </c>
       <c r="I10" s="27"/>
     </row>
-    <row r="11" spans="1:9" s="21" customFormat="1">
+    <row r="11" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="26">
         <v>5001016149</v>
       </c>
@@ -20451,7 +20438,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="21" customFormat="1">
+    <row r="12" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="26">
         <v>5001016151</v>
       </c>
@@ -20476,7 +20463,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="21" customFormat="1">
+    <row r="13" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="26">
         <v>5004046221</v>
       </c>
@@ -20499,7 +20486,7 @@
       <c r="H13" s="29"/>
       <c r="I13" s="27"/>
     </row>
-    <row r="14" spans="1:9" s="21" customFormat="1">
+    <row r="14" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="26">
         <v>5004046371</v>
       </c>
@@ -20522,7 +20509,7 @@
       <c r="H14" s="29"/>
       <c r="I14" s="27"/>
     </row>
-    <row r="15" spans="1:9" s="21" customFormat="1">
+    <row r="15" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="26">
         <v>5005016371</v>
       </c>
@@ -20545,7 +20532,7 @@
       <c r="H15" s="29"/>
       <c r="I15" s="27"/>
     </row>
-    <row r="16" spans="1:9" s="21" customFormat="1">
+    <row r="16" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="26">
         <v>5005016372</v>
       </c>
@@ -20568,7 +20555,7 @@
       <c r="H16" s="29"/>
       <c r="I16" s="27"/>
     </row>
-    <row r="17" spans="1:9" s="21" customFormat="1">
+    <row r="17" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="26">
         <v>5005016373</v>
       </c>
@@ -20593,7 +20580,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="21" customFormat="1">
+    <row r="18" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="26">
         <v>5005026371</v>
       </c>
@@ -20616,7 +20603,7 @@
       <c r="H18" s="29"/>
       <c r="I18" s="27"/>
     </row>
-    <row r="19" spans="1:9" s="21" customFormat="1">
+    <row r="19" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="26">
         <v>5005026372</v>
       </c>
@@ -20639,7 +20626,7 @@
       <c r="H19" s="29"/>
       <c r="I19" s="27"/>
     </row>
-    <row r="20" spans="1:9" s="21" customFormat="1">
+    <row r="20" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="26">
         <v>5006016241</v>
       </c>
@@ -20662,7 +20649,7 @@
       <c r="H20" s="29"/>
       <c r="I20" s="27"/>
     </row>
-    <row r="21" spans="1:9" s="21" customFormat="1">
+    <row r="21" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="26">
         <v>5006016242</v>
       </c>
@@ -20685,7 +20672,7 @@
       <c r="H21" s="29"/>
       <c r="I21" s="27"/>
     </row>
-    <row r="22" spans="1:9" s="21" customFormat="1">
+    <row r="22" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="26">
         <v>5006016243</v>
       </c>
@@ -20708,7 +20695,7 @@
       <c r="H22" s="29"/>
       <c r="I22" s="27"/>
     </row>
-    <row r="23" spans="1:9" s="21" customFormat="1">
+    <row r="23" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="26">
         <v>5006016244</v>
       </c>
@@ -20731,7 +20718,7 @@
       <c r="H23" s="29"/>
       <c r="I23" s="27"/>
     </row>
-    <row r="24" spans="1:9" s="21" customFormat="1">
+    <row r="24" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="26">
         <v>5006016245</v>
       </c>
@@ -20754,7 +20741,7 @@
       <c r="H24" s="29"/>
       <c r="I24" s="27"/>
     </row>
-    <row r="25" spans="1:9" s="21" customFormat="1">
+    <row r="25" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="26">
         <v>5005036246</v>
       </c>
@@ -20777,7 +20764,7 @@
       <c r="H25" s="29"/>
       <c r="I25" s="27"/>
     </row>
-    <row r="26" spans="1:9" s="21" customFormat="1">
+    <row r="26" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="26">
         <v>5006016247</v>
       </c>
@@ -20800,7 +20787,7 @@
       <c r="H26" s="29"/>
       <c r="I26" s="27"/>
     </row>
-    <row r="27" spans="1:9" s="21" customFormat="1">
+    <row r="27" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="26">
         <v>5006016248</v>
       </c>
@@ -20823,7 +20810,7 @@
       <c r="H27" s="29"/>
       <c r="I27" s="27"/>
     </row>
-    <row r="28" spans="1:9" s="21" customFormat="1">
+    <row r="28" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="26">
         <v>5006016249</v>
       </c>
@@ -20846,7 +20833,7 @@
       <c r="H28" s="29"/>
       <c r="I28" s="27"/>
     </row>
-    <row r="29" spans="1:9" s="21" customFormat="1">
+    <row r="29" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="26">
         <v>5006016250</v>
       </c>
@@ -20869,7 +20856,7 @@
       <c r="H29" s="29"/>
       <c r="I29" s="27"/>
     </row>
-    <row r="30" spans="1:9" s="21" customFormat="1">
+    <row r="30" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="26">
         <v>5006016251</v>
       </c>
@@ -20892,7 +20879,7 @@
       <c r="H30" s="29"/>
       <c r="I30" s="27"/>
     </row>
-    <row r="31" spans="1:9" s="21" customFormat="1">
+    <row r="31" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="26">
         <v>5006016252</v>
       </c>
@@ -20915,7 +20902,7 @@
       <c r="H31" s="29"/>
       <c r="I31" s="27"/>
     </row>
-    <row r="32" spans="1:9" s="21" customFormat="1">
+    <row r="32" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="26">
         <v>5006016253</v>
       </c>
@@ -20938,7 +20925,7 @@
       <c r="H32" s="29"/>
       <c r="I32" s="27"/>
     </row>
-    <row r="33" spans="1:9" s="21" customFormat="1">
+    <row r="33" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="26">
         <v>5006016254</v>
       </c>
@@ -20961,7 +20948,7 @@
       <c r="H33" s="29"/>
       <c r="I33" s="27"/>
     </row>
-    <row r="34" spans="1:9" s="21" customFormat="1">
+    <row r="34" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="26">
         <v>5006016255</v>
       </c>
@@ -20984,7 +20971,7 @@
       <c r="H34" s="29"/>
       <c r="I34" s="27"/>
     </row>
-    <row r="35" spans="1:9" s="21" customFormat="1">
+    <row r="35" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="26">
         <v>5006016256</v>
       </c>
@@ -21007,7 +20994,7 @@
       <c r="H35" s="29"/>
       <c r="I35" s="27"/>
     </row>
-    <row r="36" spans="1:9" s="21" customFormat="1">
+    <row r="36" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="26">
         <v>5006016257</v>
       </c>
@@ -21030,7 +21017,7 @@
       <c r="H36" s="29"/>
       <c r="I36" s="27"/>
     </row>
-    <row r="37" spans="1:9" s="21" customFormat="1">
+    <row r="37" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="26">
         <v>5006016258</v>
       </c>
@@ -21053,7 +21040,7 @@
       <c r="H37" s="29"/>
       <c r="I37" s="27"/>
     </row>
-    <row r="38" spans="1:9" s="21" customFormat="1">
+    <row r="38" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="26">
         <v>5006016259</v>
       </c>
@@ -21076,7 +21063,7 @@
       <c r="H38" s="29"/>
       <c r="I38" s="27"/>
     </row>
-    <row r="39" spans="1:9" s="21" customFormat="1">
+    <row r="39" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="26">
         <v>5006016260</v>
       </c>
@@ -21099,7 +21086,7 @@
       <c r="H39" s="29"/>
       <c r="I39" s="27"/>
     </row>
-    <row r="40" spans="1:9" s="21" customFormat="1">
+    <row r="40" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="26">
         <v>5006016261</v>
       </c>
@@ -21122,7 +21109,7 @@
       <c r="H40" s="29"/>
       <c r="I40" s="27"/>
     </row>
-    <row r="41" spans="1:9" s="21" customFormat="1">
+    <row r="41" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="26">
         <v>5004096281</v>
       </c>
@@ -21145,7 +21132,7 @@
       <c r="H41" s="29"/>
       <c r="I41" s="27"/>
     </row>
-    <row r="42" spans="1:9" s="21" customFormat="1">
+    <row r="42" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="26">
         <v>5005046281</v>
       </c>
@@ -21168,7 +21155,7 @@
       <c r="H42" s="29"/>
       <c r="I42" s="27"/>
     </row>
-    <row r="43" spans="1:9" s="21" customFormat="1">
+    <row r="43" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="26">
         <v>5005046282</v>
       </c>
@@ -21191,7 +21178,7 @@
       <c r="H43" s="29"/>
       <c r="I43" s="27"/>
     </row>
-    <row r="44" spans="1:9" s="21" customFormat="1">
+    <row r="44" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="26">
         <v>5005046283</v>
       </c>
@@ -21214,7 +21201,7 @@
       <c r="H44" s="29"/>
       <c r="I44" s="27"/>
     </row>
-    <row r="45" spans="1:9" s="21" customFormat="1">
+    <row r="45" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="26">
         <v>5005046284</v>
       </c>
@@ -21239,7 +21226,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="46" spans="1:9" s="21" customFormat="1">
+    <row r="46" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="26">
         <v>5005066281</v>
       </c>
@@ -21262,7 +21249,7 @@
       <c r="H46" s="29"/>
       <c r="I46" s="27"/>
     </row>
-    <row r="47" spans="1:9" s="21" customFormat="1">
+    <row r="47" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="26">
         <v>5005066282</v>
       </c>
@@ -21285,7 +21272,7 @@
       <c r="H47" s="29"/>
       <c r="I47" s="27"/>
     </row>
-    <row r="48" spans="1:9" s="21" customFormat="1">
+    <row r="48" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="26">
         <v>5005056281</v>
       </c>
@@ -21308,7 +21295,7 @@
       <c r="H48" s="29"/>
       <c r="I48" s="27"/>
     </row>
-    <row r="49" spans="1:9" s="21" customFormat="1">
+    <row r="49" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="26">
         <v>5005076281</v>
       </c>
@@ -21331,7 +21318,7 @@
       <c r="H49" s="29"/>
       <c r="I49" s="27"/>
     </row>
-    <row r="50" spans="1:9" s="21" customFormat="1">
+    <row r="50" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="26">
         <v>5005076282</v>
       </c>
@@ -21354,7 +21341,7 @@
       <c r="H50" s="29"/>
       <c r="I50" s="27"/>
     </row>
-    <row r="51" spans="1:9" s="21" customFormat="1">
+    <row r="51" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="26">
         <v>5005076283</v>
       </c>
@@ -21377,7 +21364,7 @@
       <c r="H51" s="29"/>
       <c r="I51" s="27"/>
     </row>
-    <row r="52" spans="1:9" s="21" customFormat="1">
+    <row r="52" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="26">
         <v>5005076284</v>
       </c>
@@ -21400,7 +21387,7 @@
       <c r="H52" s="29"/>
       <c r="I52" s="27"/>
     </row>
-    <row r="53" spans="1:9" s="21" customFormat="1">
+    <row r="53" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="26">
         <v>5005076285</v>
       </c>
@@ -21423,7 +21410,7 @@
       <c r="H53" s="29"/>
       <c r="I53" s="27"/>
     </row>
-    <row r="54" spans="1:9" s="21" customFormat="1">
+    <row r="54" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="26">
         <v>5005076286</v>
       </c>
@@ -21446,7 +21433,7 @@
       <c r="H54" s="29"/>
       <c r="I54" s="27"/>
     </row>
-    <row r="55" spans="1:9" s="21" customFormat="1">
+    <row r="55" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="26">
         <v>5005076287</v>
       </c>
@@ -21469,7 +21456,7 @@
       <c r="H55" s="29"/>
       <c r="I55" s="27"/>
     </row>
-    <row r="56" spans="1:9" s="21" customFormat="1">
+    <row r="56" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="26">
         <v>5005076288</v>
       </c>
@@ -21492,7 +21479,7 @@
       <c r="H56" s="29"/>
       <c r="I56" s="27"/>
     </row>
-    <row r="57" spans="1:9" s="21" customFormat="1">
+    <row r="57" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="26">
         <v>5005076289</v>
       </c>
@@ -21515,7 +21502,7 @@
       <c r="H57" s="29"/>
       <c r="I57" s="27"/>
     </row>
-    <row r="58" spans="1:9" s="21" customFormat="1">
+    <row r="58" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="26">
         <v>5005076291</v>
       </c>
@@ -21540,7 +21527,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="59" spans="1:9" s="21" customFormat="1">
+    <row r="59" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="26">
         <v>5005076292</v>
       </c>
@@ -21565,7 +21552,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="60" spans="1:9" s="21" customFormat="1">
+    <row r="60" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="26">
         <v>5005076293</v>
       </c>
@@ -21590,7 +21577,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="61" spans="1:9" s="21" customFormat="1">
+    <row r="61" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="26">
         <v>5005076294</v>
       </c>
@@ -21615,7 +21602,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="62" spans="1:9" s="21" customFormat="1">
+    <row r="62" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="26">
         <v>5005086281</v>
       </c>
@@ -21638,7 +21625,7 @@
       <c r="H62" s="29"/>
       <c r="I62" s="27"/>
     </row>
-    <row r="63" spans="1:9" s="21" customFormat="1">
+    <row r="63" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="26">
         <v>5005136281</v>
       </c>
@@ -21661,7 +21648,7 @@
       <c r="H63" s="29"/>
       <c r="I63" s="27"/>
     </row>
-    <row r="64" spans="1:9" s="21" customFormat="1">
+    <row r="64" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="26">
         <v>5005246281</v>
       </c>
@@ -21684,7 +21671,7 @@
       <c r="H64" s="29"/>
       <c r="I64" s="27"/>
     </row>
-    <row r="65" spans="1:9" s="21" customFormat="1">
+    <row r="65" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="26">
         <v>5005246282</v>
       </c>
@@ -21707,7 +21694,7 @@
       <c r="H65" s="29"/>
       <c r="I65" s="27"/>
     </row>
-    <row r="66" spans="1:9" s="21" customFormat="1">
+    <row r="66" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="26">
         <v>5005246283</v>
       </c>
@@ -21730,7 +21717,7 @@
       <c r="H66" s="29"/>
       <c r="I66" s="27"/>
     </row>
-    <row r="67" spans="1:9" s="21" customFormat="1">
+    <row r="67" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="26">
         <v>5005246284</v>
       </c>
@@ -21753,7 +21740,7 @@
       <c r="H67" s="29"/>
       <c r="I67" s="27"/>
     </row>
-    <row r="68" spans="1:9" s="21" customFormat="1">
+    <row r="68" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="26">
         <v>5005216281</v>
       </c>
@@ -21776,7 +21763,7 @@
       <c r="H68" s="29"/>
       <c r="I68" s="27"/>
     </row>
-    <row r="69" spans="1:9" s="21" customFormat="1">
+    <row r="69" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="26">
         <v>5005226281</v>
       </c>
@@ -21799,7 +21786,7 @@
       <c r="H69" s="29"/>
       <c r="I69" s="27"/>
     </row>
-    <row r="70" spans="1:9" s="21" customFormat="1">
+    <row r="70" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="26">
         <v>5005236281</v>
       </c>
@@ -21822,7 +21809,7 @@
       <c r="H70" s="29"/>
       <c r="I70" s="27"/>
     </row>
-    <row r="71" spans="1:9" s="21" customFormat="1">
+    <row r="71" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="26">
         <v>5005236282</v>
       </c>
@@ -21845,7 +21832,7 @@
       <c r="H71" s="29"/>
       <c r="I71" s="27"/>
     </row>
-    <row r="72" spans="1:9" s="21" customFormat="1">
+    <row r="72" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="26">
         <v>5005246285</v>
       </c>
@@ -21868,7 +21855,7 @@
       <c r="H72" s="29"/>
       <c r="I72" s="27"/>
     </row>
-    <row r="73" spans="1:9" s="21" customFormat="1">
+    <row r="73" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="26">
         <v>5005246286</v>
       </c>
@@ -21891,7 +21878,7 @@
       <c r="H73" s="29"/>
       <c r="I73" s="27"/>
     </row>
-    <row r="74" spans="1:9" s="21" customFormat="1">
+    <row r="74" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="26">
         <v>5005246287</v>
       </c>
@@ -21914,7 +21901,7 @@
       <c r="H74" s="29"/>
       <c r="I74" s="27"/>
     </row>
-    <row r="75" spans="1:9" s="21" customFormat="1">
+    <row r="75" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="26">
         <v>5005246288</v>
       </c>
@@ -21937,7 +21924,7 @@
       <c r="H75" s="29"/>
       <c r="I75" s="27"/>
     </row>
-    <row r="76" spans="1:9" s="21" customFormat="1">
+    <row r="76" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="26">
         <v>5004086291</v>
       </c>
@@ -21960,7 +21947,7 @@
       <c r="H76" s="29"/>
       <c r="I76" s="27"/>
     </row>
-    <row r="77" spans="1:9" s="21" customFormat="1">
+    <row r="77" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="26">
         <v>5004086293</v>
       </c>
@@ -21983,7 +21970,7 @@
       <c r="H77" s="29"/>
       <c r="I77" s="27"/>
     </row>
-    <row r="78" spans="1:9" s="21" customFormat="1">
+    <row r="78" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="26">
         <v>5005116291</v>
       </c>
@@ -22006,7 +21993,7 @@
       <c r="H78" s="29"/>
       <c r="I78" s="27"/>
     </row>
-    <row r="79" spans="1:9" s="21" customFormat="1">
+    <row r="79" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="26">
         <v>5005116292</v>
       </c>
@@ -22029,7 +22016,7 @@
       <c r="H79" s="29"/>
       <c r="I79" s="27"/>
     </row>
-    <row r="80" spans="1:9" s="21" customFormat="1">
+    <row r="80" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="26">
         <v>5005136291</v>
       </c>
@@ -22052,7 +22039,7 @@
       <c r="H80" s="29"/>
       <c r="I80" s="27"/>
     </row>
-    <row r="81" spans="1:9" s="21" customFormat="1">
+    <row r="81" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="26">
         <v>5005166291</v>
       </c>
@@ -22075,7 +22062,7 @@
       <c r="H81" s="29"/>
       <c r="I81" s="27"/>
     </row>
-    <row r="82" spans="1:9" s="21" customFormat="1">
+    <row r="82" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="26">
         <v>5005186292</v>
       </c>
@@ -22098,7 +22085,7 @@
       <c r="H82" s="29"/>
       <c r="I82" s="27"/>
     </row>
-    <row r="83" spans="1:9" s="21" customFormat="1">
+    <row r="83" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="26">
         <v>5005196373</v>
       </c>
@@ -22127,7 +22114,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="84" spans="1:9" s="21" customFormat="1">
+    <row r="84" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="26">
         <v>5005196277</v>
       </c>
@@ -22156,7 +22143,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="85" spans="1:9" s="21" customFormat="1">
+    <row r="85" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="26">
         <v>5005246291</v>
       </c>
@@ -22179,7 +22166,7 @@
       <c r="H85" s="29"/>
       <c r="I85" s="27"/>
     </row>
-    <row r="86" spans="1:9" s="21" customFormat="1">
+    <row r="86" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="26">
         <v>5005246292</v>
       </c>
@@ -22202,7 +22189,7 @@
       <c r="H86" s="29"/>
       <c r="I86" s="27"/>
     </row>
-    <row r="87" spans="1:9" s="21" customFormat="1">
+    <row r="87" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="26">
         <v>5005246294</v>
       </c>
@@ -22227,7 +22214,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="88" spans="1:9" s="21" customFormat="1">
+    <row r="88" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="26">
         <v>5005256291</v>
       </c>
@@ -22250,7 +22237,7 @@
       <c r="H88" s="29"/>
       <c r="I88" s="27"/>
     </row>
-    <row r="89" spans="1:9" s="21" customFormat="1">
+    <row r="89" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="26">
         <v>5101016174</v>
       </c>
@@ -22273,7 +22260,7 @@
       <c r="H89" s="29"/>
       <c r="I89" s="27"/>
     </row>
-    <row r="90" spans="1:9" s="21" customFormat="1">
+    <row r="90" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="26">
         <v>5101016179</v>
       </c>
@@ -22296,7 +22283,7 @@
       <c r="H90" s="29"/>
       <c r="I90" s="27"/>
     </row>
-    <row r="91" spans="1:9" s="21" customFormat="1">
+    <row r="91" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="26">
         <v>5101016187</v>
       </c>
@@ -22319,7 +22306,7 @@
       <c r="H91" s="29"/>
       <c r="I91" s="27"/>
     </row>
-    <row r="92" spans="1:9" s="21" customFormat="1">
+    <row r="92" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="26">
         <v>5101016189</v>
       </c>
@@ -22344,7 +22331,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="93" spans="1:9" s="21" customFormat="1">
+    <row r="93" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="26">
         <v>6004046511</v>
       </c>
@@ -22367,7 +22354,7 @@
       </c>
       <c r="I93" s="27"/>
     </row>
-    <row r="94" spans="1:9" s="21" customFormat="1">
+    <row r="94" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="26">
         <v>6003036412</v>
       </c>
@@ -22390,7 +22377,7 @@
       </c>
       <c r="I94" s="27"/>
     </row>
-    <row r="95" spans="1:9" s="21" customFormat="1">
+    <row r="95" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="26">
         <v>6005016413</v>
       </c>
@@ -22413,7 +22400,7 @@
       </c>
       <c r="I95" s="27"/>
     </row>
-    <row r="96" spans="1:9" s="21" customFormat="1">
+    <row r="96" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="26">
         <v>6005016414</v>
       </c>
@@ -22440,7 +22427,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="97" spans="1:9" s="21" customFormat="1">
+    <row r="97" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="26">
         <v>6006016521</v>
       </c>
@@ -22463,7 +22450,7 @@
       </c>
       <c r="I97" s="27"/>
     </row>
-    <row r="98" spans="1:9" s="21" customFormat="1">
+    <row r="98" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="26">
         <v>6006016522</v>
       </c>
@@ -22486,7 +22473,7 @@
       </c>
       <c r="I98" s="27"/>
     </row>
-    <row r="99" spans="1:9" s="21" customFormat="1">
+    <row r="99" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="26">
         <v>6006016523</v>
       </c>
@@ -22509,7 +22496,7 @@
       </c>
       <c r="I99" s="27"/>
     </row>
-    <row r="100" spans="1:9" s="21" customFormat="1">
+    <row r="100" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="26">
         <v>6006016524</v>
       </c>
@@ -22532,7 +22519,7 @@
       </c>
       <c r="I100" s="27"/>
     </row>
-    <row r="101" spans="1:9" s="21" customFormat="1">
+    <row r="101" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="26">
         <v>6006016525</v>
       </c>
@@ -22555,7 +22542,7 @@
       </c>
       <c r="I101" s="27"/>
     </row>
-    <row r="102" spans="1:9" s="21" customFormat="1">
+    <row r="102" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="26">
         <v>6006016526</v>
       </c>
@@ -22578,7 +22565,7 @@
       </c>
       <c r="I102" s="27"/>
     </row>
-    <row r="103" spans="1:9" s="21" customFormat="1">
+    <row r="103" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="26">
         <v>6006016527</v>
       </c>
@@ -22601,7 +22588,7 @@
       </c>
       <c r="I103" s="27"/>
     </row>
-    <row r="104" spans="1:9" s="21" customFormat="1">
+    <row r="104" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="26">
         <v>6006016528</v>
       </c>
@@ -22624,7 +22611,7 @@
       </c>
       <c r="I104" s="27"/>
     </row>
-    <row r="105" spans="1:9" s="21" customFormat="1">
+    <row r="105" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="26">
         <v>6006016529</v>
       </c>
@@ -22647,7 +22634,7 @@
       </c>
       <c r="I105" s="27"/>
     </row>
-    <row r="106" spans="1:9" s="21" customFormat="1">
+    <row r="106" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="26">
         <v>6006016530</v>
       </c>
@@ -22670,7 +22657,7 @@
       </c>
       <c r="I106" s="27"/>
     </row>
-    <row r="107" spans="1:9" s="21" customFormat="1">
+    <row r="107" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="26">
         <v>6006016531</v>
       </c>
@@ -22693,7 +22680,7 @@
       </c>
       <c r="I107" s="27"/>
     </row>
-    <row r="108" spans="1:9" s="21" customFormat="1">
+    <row r="108" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="26">
         <v>6006016532</v>
       </c>
@@ -22716,7 +22703,7 @@
       </c>
       <c r="I108" s="27"/>
     </row>
-    <row r="109" spans="1:9" s="21" customFormat="1">
+    <row r="109" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="26">
         <v>6006016533</v>
       </c>
@@ -22739,7 +22726,7 @@
       </c>
       <c r="I109" s="27"/>
     </row>
-    <row r="110" spans="1:9" s="21" customFormat="1">
+    <row r="110" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="26">
         <v>6006016534</v>
       </c>
@@ -22762,7 +22749,7 @@
       </c>
       <c r="I110" s="27"/>
     </row>
-    <row r="111" spans="1:9" s="21" customFormat="1">
+    <row r="111" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="26">
         <v>6006016535</v>
       </c>
@@ -22785,7 +22772,7 @@
       </c>
       <c r="I111" s="27"/>
     </row>
-    <row r="112" spans="1:9" s="21" customFormat="1">
+    <row r="112" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="26">
         <v>6006016536</v>
       </c>
@@ -22808,7 +22795,7 @@
       </c>
       <c r="I112" s="27"/>
     </row>
-    <row r="113" spans="1:9" s="21" customFormat="1">
+    <row r="113" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="26">
         <v>6006016537</v>
       </c>
@@ -22831,7 +22818,7 @@
       </c>
       <c r="I113" s="27"/>
     </row>
-    <row r="114" spans="1:9" s="21" customFormat="1">
+    <row r="114" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="26">
         <v>6006016538</v>
       </c>
@@ -22854,7 +22841,7 @@
       </c>
       <c r="I114" s="27"/>
     </row>
-    <row r="115" spans="1:9" s="21" customFormat="1">
+    <row r="115" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="26">
         <v>6006016539</v>
       </c>
@@ -22877,7 +22864,7 @@
       </c>
       <c r="I115" s="27"/>
     </row>
-    <row r="116" spans="1:9" s="21" customFormat="1">
+    <row r="116" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="26">
         <v>6006016540</v>
       </c>
@@ -22900,7 +22887,7 @@
       </c>
       <c r="I116" s="27"/>
     </row>
-    <row r="117" spans="1:9" s="21" customFormat="1">
+    <row r="117" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="26">
         <v>6005046541</v>
       </c>
@@ -22923,7 +22910,7 @@
       </c>
       <c r="I117" s="27"/>
     </row>
-    <row r="118" spans="1:9" s="21" customFormat="1">
+    <row r="118" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="26">
         <v>6005046542</v>
       </c>
@@ -22946,7 +22933,7 @@
       </c>
       <c r="I118" s="27"/>
     </row>
-    <row r="119" spans="1:9" s="21" customFormat="1">
+    <row r="119" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="26">
         <v>6003016541</v>
       </c>
@@ -22969,7 +22956,7 @@
       </c>
       <c r="I119" s="27"/>
     </row>
-    <row r="120" spans="1:9" s="21" customFormat="1">
+    <row r="120" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="26">
         <v>6003026541</v>
       </c>
@@ -22992,7 +22979,7 @@
       </c>
       <c r="I120" s="27"/>
     </row>
-    <row r="121" spans="1:9" s="21" customFormat="1">
+    <row r="121" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="26">
         <v>6003036541</v>
       </c>
@@ -23015,7 +23002,7 @@
       </c>
       <c r="I121" s="27"/>
     </row>
-    <row r="122" spans="1:9" s="21" customFormat="1">
+    <row r="122" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="26">
         <v>6003036542</v>
       </c>
@@ -23038,7 +23025,7 @@
       </c>
       <c r="I122" s="27"/>
     </row>
-    <row r="123" spans="1:9" s="21" customFormat="1">
+    <row r="123" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="26">
         <v>6003036543</v>
       </c>
@@ -23063,7 +23050,7 @@
       </c>
       <c r="I123" s="27"/>
     </row>
-    <row r="124" spans="1:9" s="21" customFormat="1">
+    <row r="124" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="26">
         <v>6003036544</v>
       </c>
@@ -23090,7 +23077,7 @@
       </c>
       <c r="I124" s="27"/>
     </row>
-    <row r="125" spans="1:9" s="21" customFormat="1">
+    <row r="125" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="26">
         <v>6003036545</v>
       </c>
@@ -23113,7 +23100,7 @@
       </c>
       <c r="I125" s="27"/>
     </row>
-    <row r="126" spans="1:9" s="21" customFormat="1">
+    <row r="126" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="26">
         <v>6003036546</v>
       </c>
@@ -23136,7 +23123,7 @@
       </c>
       <c r="I126" s="27"/>
     </row>
-    <row r="127" spans="1:9" s="21" customFormat="1">
+    <row r="127" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="26">
         <v>6003036547</v>
       </c>
@@ -23159,7 +23146,7 @@
       </c>
       <c r="I127" s="27"/>
     </row>
-    <row r="128" spans="1:9" s="21" customFormat="1">
+    <row r="128" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="26">
         <v>6003036548</v>
       </c>
@@ -23182,7 +23169,7 @@
       </c>
       <c r="I128" s="27"/>
     </row>
-    <row r="129" spans="1:9" s="21" customFormat="1">
+    <row r="129" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="26">
         <v>6003036549</v>
       </c>
@@ -23205,7 +23192,7 @@
       </c>
       <c r="I129" s="27"/>
     </row>
-    <row r="130" spans="1:9" s="21" customFormat="1">
+    <row r="130" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="26">
         <v>6003036550</v>
       </c>
@@ -23228,7 +23215,7 @@
       </c>
       <c r="I130" s="27"/>
     </row>
-    <row r="131" spans="1:9" s="21" customFormat="1">
+    <row r="131" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="26">
         <v>6003036551</v>
       </c>
@@ -23251,7 +23238,7 @@
       </c>
       <c r="I131" s="27"/>
     </row>
-    <row r="132" spans="1:9" s="21" customFormat="1">
+    <row r="132" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="26">
         <v>6003036552</v>
       </c>
@@ -23276,7 +23263,7 @@
       </c>
       <c r="I132" s="27"/>
     </row>
-    <row r="133" spans="1:9" s="21" customFormat="1">
+    <row r="133" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="26">
         <v>6003036554</v>
       </c>
@@ -23305,7 +23292,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="134" spans="1:9" s="21" customFormat="1">
+    <row r="134" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="26">
         <v>6003036555</v>
       </c>
@@ -23334,7 +23321,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="135" spans="1:9" s="21" customFormat="1">
+    <row r="135" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="26">
         <v>6003036556</v>
       </c>
@@ -23363,7 +23350,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="136" spans="1:9" s="21" customFormat="1">
+    <row r="136" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="26">
         <v>6003036557</v>
       </c>
@@ -23392,7 +23379,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="137" spans="1:9" s="21" customFormat="1">
+    <row r="137" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="26">
         <v>6004096541</v>
       </c>
@@ -23415,7 +23402,7 @@
       </c>
       <c r="I137" s="27"/>
     </row>
-    <row r="138" spans="1:9" s="21" customFormat="1">
+    <row r="138" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="26">
         <v>6005056541</v>
       </c>
@@ -23438,7 +23425,7 @@
       </c>
       <c r="I138" s="27"/>
     </row>
-    <row r="139" spans="1:9" s="21" customFormat="1">
+    <row r="139" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="26">
         <v>6005056542</v>
       </c>
@@ -23461,7 +23448,7 @@
       </c>
       <c r="I139" s="27"/>
     </row>
-    <row r="140" spans="1:9" s="21" customFormat="1">
+    <row r="140" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="26">
         <v>6005056543</v>
       </c>
@@ -23484,7 +23471,7 @@
       </c>
       <c r="I140" s="27"/>
     </row>
-    <row r="141" spans="1:9" s="21" customFormat="1">
+    <row r="141" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="26">
         <v>6005136541</v>
       </c>
@@ -23507,7 +23494,7 @@
       </c>
       <c r="I141" s="27"/>
     </row>
-    <row r="142" spans="1:9" s="21" customFormat="1">
+    <row r="142" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="26">
         <v>6005146541</v>
       </c>
@@ -23530,7 +23517,7 @@
       </c>
       <c r="I142" s="27"/>
     </row>
-    <row r="143" spans="1:9" s="21" customFormat="1">
+    <row r="143" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="26">
         <v>6005146542</v>
       </c>
@@ -23553,7 +23540,7 @@
       </c>
       <c r="I143" s="27"/>
     </row>
-    <row r="144" spans="1:9" s="21" customFormat="1">
+    <row r="144" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="26">
         <v>6005146543</v>
       </c>
@@ -23576,7 +23563,7 @@
       </c>
       <c r="I144" s="27"/>
     </row>
-    <row r="145" spans="1:9" s="21" customFormat="1">
+    <row r="145" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="26">
         <v>6005156541</v>
       </c>
@@ -23599,7 +23586,7 @@
       </c>
       <c r="I145" s="27"/>
     </row>
-    <row r="146" spans="1:9" s="21" customFormat="1">
+    <row r="146" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="26">
         <v>6005206541</v>
       </c>
@@ -23622,7 +23609,7 @@
       </c>
       <c r="I146" s="27"/>
     </row>
-    <row r="147" spans="1:9" s="21" customFormat="1">
+    <row r="147" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="26">
         <v>6005216541</v>
       </c>
@@ -23645,7 +23632,7 @@
       </c>
       <c r="I147" s="27"/>
     </row>
-    <row r="148" spans="1:9" s="21" customFormat="1">
+    <row r="148" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="26">
         <v>6005226541</v>
       </c>
@@ -23668,7 +23655,7 @@
       </c>
       <c r="I148" s="27"/>
     </row>
-    <row r="149" spans="1:9" s="21" customFormat="1">
+    <row r="149" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="26">
         <v>6005236541</v>
       </c>
@@ -23691,7 +23678,7 @@
       </c>
       <c r="I149" s="27"/>
     </row>
-    <row r="150" spans="1:9" s="21" customFormat="1">
+    <row r="150" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="26">
         <v>6005246541</v>
       </c>
@@ -23714,7 +23701,7 @@
       </c>
       <c r="I150" s="27"/>
     </row>
-    <row r="151" spans="1:9" s="21" customFormat="1">
+    <row r="151" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="26">
         <v>6005246542</v>
       </c>
@@ -23741,7 +23728,7 @@
       </c>
       <c r="I151" s="27"/>
     </row>
-    <row r="152" spans="1:9" s="21" customFormat="1">
+    <row r="152" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="26">
         <v>6005246543</v>
       </c>
@@ -23768,7 +23755,7 @@
       </c>
       <c r="I152" s="27"/>
     </row>
-    <row r="153" spans="1:9" s="21" customFormat="1">
+    <row r="153" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="26">
         <v>6005246544</v>
       </c>
@@ -23791,7 +23778,7 @@
       </c>
       <c r="I153" s="27"/>
     </row>
-    <row r="154" spans="1:9" s="21" customFormat="1">
+    <row r="154" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="26">
         <v>6004086551</v>
       </c>
@@ -23814,7 +23801,7 @@
       </c>
       <c r="I154" s="27"/>
     </row>
-    <row r="155" spans="1:9" s="21" customFormat="1">
+    <row r="155" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="26">
         <v>6004086553</v>
       </c>
@@ -23837,7 +23824,7 @@
       </c>
       <c r="I155" s="27"/>
     </row>
-    <row r="156" spans="1:9" s="21" customFormat="1">
+    <row r="156" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="26">
         <v>6005116551</v>
       </c>
@@ -23860,7 +23847,7 @@
       </c>
       <c r="I156" s="27"/>
     </row>
-    <row r="157" spans="1:9" s="21" customFormat="1">
+    <row r="157" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="26">
         <v>6005116552</v>
       </c>
@@ -23883,7 +23870,7 @@
       </c>
       <c r="I157" s="27"/>
     </row>
-    <row r="158" spans="1:9" s="21" customFormat="1">
+    <row r="158" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="26">
         <v>6005136551</v>
       </c>
@@ -23906,7 +23893,7 @@
       </c>
       <c r="I158" s="27"/>
     </row>
-    <row r="159" spans="1:9" s="21" customFormat="1">
+    <row r="159" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="26">
         <v>6005166551</v>
       </c>
@@ -23929,7 +23916,7 @@
       </c>
       <c r="I159" s="27"/>
     </row>
-    <row r="160" spans="1:9" s="21" customFormat="1">
+    <row r="160" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="26">
         <v>6005186552</v>
       </c>
@@ -23952,7 +23939,7 @@
       </c>
       <c r="I160" s="27"/>
     </row>
-    <row r="161" spans="1:9" s="21" customFormat="1">
+    <row r="161" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="26">
         <v>6005246551</v>
       </c>
@@ -23975,7 +23962,7 @@
       </c>
       <c r="I161" s="27"/>
     </row>
-    <row r="162" spans="1:9" s="21" customFormat="1">
+    <row r="162" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="26">
         <v>6005246552</v>
       </c>
@@ -23998,7 +23985,7 @@
       </c>
       <c r="I162" s="27"/>
     </row>
-    <row r="163" spans="1:9" s="21" customFormat="1">
+    <row r="163" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="26">
         <v>6005246553</v>
       </c>
@@ -24021,7 +24008,7 @@
       </c>
       <c r="I163" s="27"/>
     </row>
-    <row r="164" spans="1:9" s="21" customFormat="1">
+    <row r="164" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="26">
         <v>6004046421</v>
       </c>
@@ -24044,7 +24031,7 @@
       <c r="H164" s="29"/>
       <c r="I164" s="27"/>
     </row>
-    <row r="165" spans="1:9" s="21" customFormat="1">
+    <row r="165" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="26">
         <v>6005016422</v>
       </c>
@@ -24069,7 +24056,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="166" spans="1:9" s="21" customFormat="1">
+    <row r="166" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="26">
         <v>6005016423</v>
       </c>
@@ -24096,7 +24083,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="167" spans="1:9" s="21" customFormat="1">
+    <row r="167" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="26">
         <v>6005126423</v>
       </c>
@@ -24119,7 +24106,7 @@
       <c r="H167" s="29"/>
       <c r="I167" s="27"/>
     </row>
-    <row r="168" spans="1:9" s="21" customFormat="1">
+    <row r="168" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="26">
         <v>6006016611</v>
       </c>
@@ -24142,7 +24129,7 @@
       <c r="H168" s="29"/>
       <c r="I168" s="27"/>
     </row>
-    <row r="169" spans="1:9" s="21" customFormat="1">
+    <row r="169" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="26">
         <v>6006016612</v>
       </c>
@@ -24165,7 +24152,7 @@
       <c r="H169" s="29"/>
       <c r="I169" s="27"/>
     </row>
-    <row r="170" spans="1:9" s="21" customFormat="1">
+    <row r="170" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="26">
         <v>6006016613</v>
       </c>
@@ -24188,7 +24175,7 @@
       <c r="H170" s="29"/>
       <c r="I170" s="27"/>
     </row>
-    <row r="171" spans="1:9" s="21" customFormat="1">
+    <row r="171" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="26">
         <v>6006016614</v>
       </c>
@@ -24211,7 +24198,7 @@
       <c r="H171" s="29"/>
       <c r="I171" s="27"/>
     </row>
-    <row r="172" spans="1:9" s="21" customFormat="1">
+    <row r="172" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="26">
         <v>6006016615</v>
       </c>
@@ -24234,7 +24221,7 @@
       <c r="H172" s="29"/>
       <c r="I172" s="27"/>
     </row>
-    <row r="173" spans="1:9" s="21" customFormat="1">
+    <row r="173" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="26">
         <v>6006016616</v>
       </c>
@@ -24257,7 +24244,7 @@
       <c r="H173" s="29"/>
       <c r="I173" s="27"/>
     </row>
-    <row r="174" spans="1:9" s="21" customFormat="1">
+    <row r="174" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="26">
         <v>6006016617</v>
       </c>
@@ -24280,7 +24267,7 @@
       <c r="H174" s="29"/>
       <c r="I174" s="27"/>
     </row>
-    <row r="175" spans="1:9" s="21" customFormat="1">
+    <row r="175" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="26">
         <v>6006016618</v>
       </c>
@@ -24303,7 +24290,7 @@
       <c r="H175" s="29"/>
       <c r="I175" s="27"/>
     </row>
-    <row r="176" spans="1:9" s="21" customFormat="1">
+    <row r="176" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="26">
         <v>6006016619</v>
       </c>
@@ -24326,7 +24313,7 @@
       <c r="H176" s="29"/>
       <c r="I176" s="27"/>
     </row>
-    <row r="177" spans="1:9" s="21" customFormat="1">
+    <row r="177" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="26">
         <v>6006016620</v>
       </c>
@@ -24349,7 +24336,7 @@
       <c r="H177" s="29"/>
       <c r="I177" s="27"/>
     </row>
-    <row r="178" spans="1:9" s="21" customFormat="1">
+    <row r="178" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="26">
         <v>6006016621</v>
       </c>
@@ -24372,7 +24359,7 @@
       <c r="H178" s="29"/>
       <c r="I178" s="27"/>
     </row>
-    <row r="179" spans="1:9" s="21" customFormat="1">
+    <row r="179" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="26">
         <v>6006016622</v>
       </c>
@@ -24395,7 +24382,7 @@
       <c r="H179" s="29"/>
       <c r="I179" s="27"/>
     </row>
-    <row r="180" spans="1:9" s="21" customFormat="1">
+    <row r="180" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="26">
         <v>6006016623</v>
       </c>
@@ -24418,7 +24405,7 @@
       <c r="H180" s="29"/>
       <c r="I180" s="27"/>
     </row>
-    <row r="181" spans="1:9" s="21" customFormat="1">
+    <row r="181" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="26">
         <v>6006016624</v>
       </c>
@@ -24441,7 +24428,7 @@
       <c r="H181" s="29"/>
       <c r="I181" s="27"/>
     </row>
-    <row r="182" spans="1:9" s="21" customFormat="1">
+    <row r="182" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="26">
         <v>6006016625</v>
       </c>
@@ -24464,7 +24451,7 @@
       <c r="H182" s="29"/>
       <c r="I182" s="27"/>
     </row>
-    <row r="183" spans="1:9" s="21" customFormat="1">
+    <row r="183" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="26">
         <v>6006016626</v>
       </c>
@@ -24487,7 +24474,7 @@
       <c r="H183" s="29"/>
       <c r="I183" s="27"/>
     </row>
-    <row r="184" spans="1:9" s="21" customFormat="1">
+    <row r="184" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="26">
         <v>6006016627</v>
       </c>
@@ -24510,7 +24497,7 @@
       <c r="H184" s="29"/>
       <c r="I184" s="27"/>
     </row>
-    <row r="185" spans="1:9" s="21" customFormat="1">
+    <row r="185" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="26">
         <v>6006016628</v>
       </c>
@@ -24533,7 +24520,7 @@
       <c r="H185" s="29"/>
       <c r="I185" s="27"/>
     </row>
-    <row r="186" spans="1:9" s="21" customFormat="1">
+    <row r="186" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="26">
         <v>6006016629</v>
       </c>
@@ -24556,7 +24543,7 @@
       <c r="H186" s="29"/>
       <c r="I186" s="27"/>
     </row>
-    <row r="187" spans="1:9" s="21" customFormat="1">
+    <row r="187" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="26">
         <v>6006016630</v>
       </c>
@@ -24581,7 +24568,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="188" spans="1:9" s="21" customFormat="1">
+    <row r="188" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="26">
         <v>6005186425</v>
       </c>
@@ -24604,7 +24591,7 @@
       <c r="H188" s="29"/>
       <c r="I188" s="27"/>
     </row>
-    <row r="189" spans="1:9" s="21" customFormat="1">
+    <row r="189" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="26">
         <v>6005186429</v>
       </c>
@@ -24627,7 +24614,7 @@
       <c r="H189" s="29"/>
       <c r="I189" s="27"/>
     </row>
-    <row r="190" spans="1:9" s="21" customFormat="1">
+    <row r="190" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="26">
         <v>6005266426</v>
       </c>
@@ -24650,7 +24637,7 @@
       <c r="H190" s="29"/>
       <c r="I190" s="27"/>
     </row>
-    <row r="191" spans="1:9" s="21" customFormat="1">
+    <row r="191" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="26">
         <v>6004096621</v>
       </c>
@@ -24673,7 +24660,7 @@
       <c r="H191" s="29"/>
       <c r="I191" s="27"/>
     </row>
-    <row r="192" spans="1:9" s="21" customFormat="1">
+    <row r="192" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="26">
         <v>6005046622</v>
       </c>
@@ -24696,7 +24683,7 @@
       <c r="H192" s="29"/>
       <c r="I192" s="27"/>
     </row>
-    <row r="193" spans="1:9" s="21" customFormat="1">
+    <row r="193" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="26">
         <v>6005046635</v>
       </c>
@@ -24719,7 +24706,7 @@
       <c r="H193" s="29"/>
       <c r="I193" s="27"/>
     </row>
-    <row r="194" spans="1:9" s="21" customFormat="1">
+    <row r="194" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="26">
         <v>6005056623</v>
       </c>
@@ -24742,7 +24729,7 @@
       <c r="H194" s="29"/>
       <c r="I194" s="27"/>
     </row>
-    <row r="195" spans="1:9" s="21" customFormat="1">
+    <row r="195" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="26">
         <v>6005056624</v>
       </c>
@@ -24765,7 +24752,7 @@
       <c r="H195" s="29"/>
       <c r="I195" s="27"/>
     </row>
-    <row r="196" spans="1:9" s="21" customFormat="1">
+    <row r="196" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="26">
         <v>6005056625</v>
       </c>
@@ -24788,7 +24775,7 @@
       <c r="H196" s="29"/>
       <c r="I196" s="27"/>
     </row>
-    <row r="197" spans="1:9" s="21" customFormat="1">
+    <row r="197" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="26">
         <v>6005136626</v>
       </c>
@@ -24811,7 +24798,7 @@
       <c r="H197" s="29"/>
       <c r="I197" s="27"/>
     </row>
-    <row r="198" spans="1:9" s="21" customFormat="1">
+    <row r="198" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="26">
         <v>6005146627</v>
       </c>
@@ -24834,7 +24821,7 @@
       <c r="H198" s="29"/>
       <c r="I198" s="27"/>
     </row>
-    <row r="199" spans="1:9" s="21" customFormat="1">
+    <row r="199" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="26">
         <v>6005146628</v>
       </c>
@@ -24857,7 +24844,7 @@
       <c r="H199" s="29"/>
       <c r="I199" s="27"/>
     </row>
-    <row r="200" spans="1:9" s="21" customFormat="1">
+    <row r="200" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="26">
         <v>6005146629</v>
       </c>
@@ -24880,7 +24867,7 @@
       <c r="H200" s="29"/>
       <c r="I200" s="27"/>
     </row>
-    <row r="201" spans="1:9" s="21" customFormat="1">
+    <row r="201" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="26">
         <v>6005156630</v>
       </c>
@@ -24903,7 +24890,7 @@
       <c r="H201" s="29"/>
       <c r="I201" s="27"/>
     </row>
-    <row r="202" spans="1:9" s="21" customFormat="1">
+    <row r="202" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="26">
         <v>6005206631</v>
       </c>
@@ -24926,7 +24913,7 @@
       <c r="H202" s="29"/>
       <c r="I202" s="27"/>
     </row>
-    <row r="203" spans="1:9" s="21" customFormat="1">
+    <row r="203" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="26">
         <v>6005216632</v>
       </c>
@@ -24949,7 +24936,7 @@
       <c r="H203" s="29"/>
       <c r="I203" s="27"/>
     </row>
-    <row r="204" spans="1:9" s="21" customFormat="1">
+    <row r="204" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="26">
         <v>6005226633</v>
       </c>
@@ -24972,7 +24959,7 @@
       <c r="H204" s="29"/>
       <c r="I204" s="27"/>
     </row>
-    <row r="205" spans="1:9" s="21" customFormat="1">
+    <row r="205" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="26">
         <v>6005236634</v>
       </c>
@@ -24995,7 +24982,7 @@
       <c r="H205" s="29"/>
       <c r="I205" s="27"/>
     </row>
-    <row r="206" spans="1:9" s="21" customFormat="1">
+    <row r="206" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="26">
         <v>6005246636</v>
       </c>
@@ -25018,7 +25005,7 @@
       <c r="H206" s="29"/>
       <c r="I206" s="27"/>
     </row>
-    <row r="207" spans="1:9" s="21" customFormat="1">
+    <row r="207" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="26">
         <v>6005246672</v>
       </c>
@@ -25041,7 +25028,7 @@
       <c r="H207" s="29"/>
       <c r="I207" s="27"/>
     </row>
-    <row r="208" spans="1:9" s="21" customFormat="1">
+    <row r="208" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="26">
         <v>6005246673</v>
       </c>
@@ -25064,7 +25051,7 @@
       <c r="H208" s="29"/>
       <c r="I208" s="27"/>
     </row>
-    <row r="209" spans="1:9" s="21" customFormat="1">
+    <row r="209" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="26">
         <v>6005246674</v>
       </c>
@@ -25087,7 +25074,7 @@
       <c r="H209" s="29"/>
       <c r="I209" s="27"/>
     </row>
-    <row r="210" spans="1:9" s="21" customFormat="1">
+    <row r="210" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="26">
         <v>6004086651</v>
       </c>
@@ -25110,7 +25097,7 @@
       <c r="H210" s="29"/>
       <c r="I210" s="27"/>
     </row>
-    <row r="211" spans="1:9" s="21" customFormat="1">
+    <row r="211" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="26">
         <v>6004086653</v>
       </c>
@@ -25133,7 +25120,7 @@
       <c r="H211" s="29"/>
       <c r="I211" s="27"/>
     </row>
-    <row r="212" spans="1:9" s="21" customFormat="1">
+    <row r="212" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="26">
         <v>6005116654</v>
       </c>
@@ -25156,7 +25143,7 @@
       <c r="H212" s="29"/>
       <c r="I212" s="27"/>
     </row>
-    <row r="213" spans="1:9" s="21" customFormat="1">
+    <row r="213" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="26">
         <v>6005116655</v>
       </c>
@@ -25179,7 +25166,7 @@
       <c r="H213" s="29"/>
       <c r="I213" s="27"/>
     </row>
-    <row r="214" spans="1:9" s="21" customFormat="1">
+    <row r="214" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="26">
         <v>6005136657</v>
       </c>
@@ -25202,7 +25189,7 @@
       <c r="H214" s="29"/>
       <c r="I214" s="27"/>
     </row>
-    <row r="215" spans="1:9" s="21" customFormat="1">
+    <row r="215" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="26">
         <v>6005166658</v>
       </c>
@@ -25225,7 +25212,7 @@
       <c r="H215" s="29"/>
       <c r="I215" s="27"/>
     </row>
-    <row r="216" spans="1:9" s="21" customFormat="1">
+    <row r="216" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="26">
         <v>6005176659</v>
       </c>
@@ -25248,7 +25235,7 @@
       <c r="H216" s="29"/>
       <c r="I216" s="27"/>
     </row>
-    <row r="217" spans="1:9" s="21" customFormat="1">
+    <row r="217" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="26">
         <v>6005246671</v>
       </c>
@@ -25271,7 +25258,7 @@
       <c r="H217" s="29"/>
       <c r="I217" s="27"/>
     </row>
-    <row r="218" spans="1:9" s="21" customFormat="1">
+    <row r="218" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="26">
         <v>6005246675</v>
       </c>
@@ -25294,7 +25281,7 @@
       <c r="H218" s="29"/>
       <c r="I218" s="27"/>
     </row>
-    <row r="219" spans="1:9" s="21" customFormat="1">
+    <row r="219" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219" s="26">
         <v>6005246676</v>
       </c>
@@ -25319,7 +25306,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="220" spans="1:9" s="21" customFormat="1">
+    <row r="220" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="26">
         <v>8001017111</v>
       </c>
@@ -25346,7 +25333,7 @@
       </c>
       <c r="I220" s="27"/>
     </row>
-    <row r="221" spans="1:9" s="21" customFormat="1">
+    <row r="221" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="26">
         <v>8001027111</v>
       </c>
@@ -25373,7 +25360,7 @@
       </c>
       <c r="I221" s="27"/>
     </row>
-    <row r="222" spans="1:9" s="21" customFormat="1">
+    <row r="222" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222" s="26">
         <v>8001037111</v>
       </c>
@@ -25400,7 +25387,7 @@
       </c>
       <c r="I222" s="27"/>
     </row>
-    <row r="223" spans="1:9" s="21" customFormat="1">
+    <row r="223" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="26">
         <v>7002048111</v>
       </c>
@@ -25427,7 +25414,7 @@
       </c>
       <c r="I223" s="27"/>
     </row>
-    <row r="224" spans="1:9" s="21" customFormat="1">
+    <row r="224" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A224" s="26">
         <v>7002048112</v>
       </c>
@@ -25454,7 +25441,7 @@
       </c>
       <c r="I224" s="27"/>
     </row>
-    <row r="225" spans="1:9" s="21" customFormat="1">
+    <row r="225" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="26">
         <v>8002018111</v>
       </c>
@@ -25481,7 +25468,7 @@
       </c>
       <c r="I225" s="27"/>
     </row>
-    <row r="226" spans="1:9" s="21" customFormat="1">
+    <row r="226" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="26">
         <v>8002028111</v>
       </c>
@@ -25508,7 +25495,7 @@
       </c>
       <c r="I226" s="27"/>
     </row>
-    <row r="227" spans="1:9" s="21" customFormat="1">
+    <row r="227" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="26">
         <v>8002038111</v>
       </c>
@@ -25535,7 +25522,7 @@
       </c>
       <c r="I227" s="27"/>
     </row>
-    <row r="228" spans="1:9" s="21" customFormat="1">
+    <row r="228" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="26">
         <v>9114120002</v>
       </c>
@@ -25560,7 +25547,7 @@
       </c>
       <c r="I228" s="27"/>
     </row>
-    <row r="229" spans="1:9" s="21" customFormat="1">
+    <row r="229" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="26">
         <v>9114120004</v>
       </c>
@@ -25585,7 +25572,7 @@
       </c>
       <c r="I229" s="27"/>
     </row>
-    <row r="230" spans="1:9" s="21" customFormat="1">
+    <row r="230" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="31">
         <v>9114120005</v>
       </c>
@@ -25610,7 +25597,7 @@
       </c>
       <c r="I230" s="27"/>
     </row>
-    <row r="231" spans="1:9" s="21" customFormat="1">
+    <row r="231" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="26">
         <v>9114120006</v>
       </c>
@@ -25635,7 +25622,7 @@
       </c>
       <c r="I231" s="27"/>
     </row>
-    <row r="232" spans="1:9" s="21" customFormat="1">
+    <row r="232" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="26">
         <v>9114120007</v>
       </c>
@@ -25660,7 +25647,7 @@
       </c>
       <c r="I232" s="27"/>
     </row>
-    <row r="233" spans="1:9" s="21" customFormat="1">
+    <row r="233" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="26">
         <v>9114120008</v>
       </c>
@@ -25681,7 +25668,7 @@
       <c r="H233" s="29"/>
       <c r="I233" s="27"/>
     </row>
-    <row r="234" spans="1:9" s="21" customFormat="1">
+    <row r="234" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="26">
         <v>9114120009</v>
       </c>
@@ -25706,7 +25693,7 @@
       </c>
       <c r="I234" s="27"/>
     </row>
-    <row r="235" spans="1:9" s="21" customFormat="1">
+    <row r="235" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="26">
         <v>9114120011</v>
       </c>
@@ -25731,7 +25718,7 @@
       </c>
       <c r="I235" s="27"/>
     </row>
-    <row r="236" spans="1:9" s="21" customFormat="1">
+    <row r="236" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="26">
         <v>9114120014</v>
       </c>
@@ -25756,7 +25743,7 @@
       </c>
       <c r="I236" s="27"/>
     </row>
-    <row r="237" spans="1:9" s="21" customFormat="1">
+    <row r="237" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="26">
         <v>9114120018</v>
       </c>
@@ -25781,7 +25768,7 @@
       </c>
       <c r="I237" s="27"/>
     </row>
-    <row r="238" spans="1:9" s="21" customFormat="1">
+    <row r="238" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="26">
         <v>9114120021</v>
       </c>
@@ -25806,7 +25793,7 @@
       </c>
       <c r="I238" s="27"/>
     </row>
-    <row r="239" spans="1:9" s="21" customFormat="1">
+    <row r="239" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="26">
         <v>9114120028</v>
       </c>
@@ -25831,7 +25818,7 @@
       </c>
       <c r="I239" s="27"/>
     </row>
-    <row r="240" spans="1:9" s="21" customFormat="1">
+    <row r="240" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="26">
         <v>9114120029</v>
       </c>
@@ -25856,7 +25843,7 @@
       </c>
       <c r="I240" s="27"/>
     </row>
-    <row r="241" spans="1:9" s="21" customFormat="1">
+    <row r="241" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="26">
         <v>9114120030</v>
       </c>
@@ -25881,7 +25868,7 @@
       </c>
       <c r="I241" s="27"/>
     </row>
-    <row r="242" spans="1:9" s="21" customFormat="1">
+    <row r="242" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="33"/>
       <c r="B242" s="30"/>
       <c r="C242" s="34"/>
@@ -25892,7 +25879,7 @@
       <c r="H242" s="29"/>
       <c r="I242" s="30"/>
     </row>
-    <row r="243" spans="1:9" s="21" customFormat="1">
+    <row r="243" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="33"/>
       <c r="B243" s="30"/>
       <c r="C243" s="34"/>
@@ -25902,7 +25889,7 @@
       <c r="G243" s="30"/>
       <c r="I243" s="30"/>
     </row>
-    <row r="244" spans="1:9" s="21" customFormat="1">
+    <row r="244" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="33"/>
       <c r="B244" s="30"/>
       <c r="C244" s="34"/>
